--- a/ZonasEscolares/excels/LIMA-LIMA-CHORRILLOS.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-CHORRILLOS.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3190,7 +3190,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3294,7 +3294,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3554,7 +3554,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3606,7 +3606,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3762,7 +3762,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4126,7 +4126,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4282,7 +4282,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4386,7 +4386,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4438,7 +4438,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4542,7 +4542,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4594,7 +4594,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4698,7 +4698,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4750,7 +4750,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4854,7 +4854,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4906,7 +4906,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5010,7 +5010,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5114,7 +5114,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5166,7 +5166,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5218,7 +5218,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5322,7 +5322,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5374,7 +5374,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5478,7 +5478,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5530,7 +5530,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5582,7 +5582,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5686,7 +5686,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5790,7 +5790,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5842,7 +5842,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5946,7 +5946,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/LIMA-LIMA-CHORRILLOS.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-CHORRILLOS.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>518 LOS ANGELES DE JESUS</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-12.17658</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-77.0094</v>
-      </c>
-      <c r="I2" t="n">
-        <v>278</v>
-      </c>
-      <c r="J2" t="n">
-        <v>13</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-12.17658</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-77.0094</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>278</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>VIRGEN MARIA MADRE DE LOS NIÑOS</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-12.19044</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-77.01063000000001</v>
-      </c>
-      <c r="I3" t="n">
-        <v>410</v>
-      </c>
-      <c r="J3" t="n">
-        <v>18</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-12.19044</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-77.01063</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>410</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>59 SANTA LUCIA</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-12.16549</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-77.02537</v>
-      </c>
-      <c r="I4" t="n">
-        <v>446</v>
-      </c>
-      <c r="J4" t="n">
-        <v>28</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-12.16549</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-77.02537</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>446</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>6005 GENERAL EMILIO SOYER CABERO</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-12.16355</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-77.02045</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1246</v>
-      </c>
-      <c r="J5" t="n">
-        <v>80</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-12.16355</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-77.02045</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1246</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>7066 ANDRES AVELINO CACERES</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-12.19998</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-76.99325</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1332</v>
-      </c>
-      <c r="J6" t="n">
-        <v>71</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-12.19998</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-76.99325</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1332</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>6075 JOSE MARIA ARGUEDAS</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-12.19814</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-76.98143</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1310</v>
-      </c>
-      <c r="J7" t="n">
-        <v>54</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-12.19814</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-76.98143</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1310</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>6085 BRIGIDA SILVA DE OCHOA</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-12.164653</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-77.020892</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1238</v>
-      </c>
-      <c r="J8" t="n">
-        <v>75</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-12.164653</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-77.020892</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1238</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>6090 JOSE OLAYA BALANDRA</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-12.19442</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-77.0063</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2685</v>
-      </c>
-      <c r="J9" t="n">
-        <v>113</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-12.19442</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-77.0063</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2685</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>6091 CESAR VALLEJO</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-12.18918</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-76.99095</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1470</v>
-      </c>
-      <c r="J10" t="n">
-        <v>65</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-12.18918</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-76.99095</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1470</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>6092 LOS REYES CATOLICOS</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-12.18701</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-77.01684</v>
-      </c>
-      <c r="I11" t="n">
-        <v>871</v>
-      </c>
-      <c r="J11" t="n">
-        <v>34</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-12.18701</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-77.01684</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>871</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>6094 SANTA ROSA</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-12.19016</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-77.01040999999999</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1539</v>
-      </c>
-      <c r="J12" t="n">
-        <v>78</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-12.19016</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-77.01041</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1539</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>6153 CAPITAN DEL EJERCITO PERUANO AUGUSTO JAVIER GUTIERREZ MENDOZA</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-12.1904</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-76.98690000000001</v>
-      </c>
-      <c r="I13" t="n">
-        <v>684</v>
-      </c>
-      <c r="J13" t="n">
-        <v>31</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-12.1904</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-76.9869</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>684</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>7034 ENRIQUE NERINI COLLAZOS</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-12.17172</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-77.024447</v>
-      </c>
-      <c r="I14" t="n">
-        <v>849</v>
-      </c>
-      <c r="J14" t="n">
-        <v>48</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-12.17172</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-77.024447</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>849</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>7036 ANGELICA RECHARTE CORRALES</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-12.16583</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-77.02445</v>
-      </c>
-      <c r="I15" t="n">
-        <v>788</v>
-      </c>
-      <c r="J15" t="n">
-        <v>39</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-12.16583</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-77.02445</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>788</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>7037 ARIOSTO MATELLINI ESPINOZA</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-12.16701</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-76.99938</v>
-      </c>
-      <c r="I16" t="n">
-        <v>684</v>
-      </c>
-      <c r="J16" t="n">
-        <v>36</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-12.16701</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-76.99938</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>684</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>7038 CORAZON DE JESUS DE ARMATAMBO</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-12.1789</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-77.02239</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1067</v>
-      </c>
-      <c r="J17" t="n">
-        <v>54</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-12.1789</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-77.02239</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1067</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>7039 MANUEL SCORZA TORRES</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-12.18322</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-76.9927</v>
-      </c>
-      <c r="I18" t="n">
-        <v>1372</v>
-      </c>
-      <c r="J18" t="n">
-        <v>70</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-12.18322</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-76.9927</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1372</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>7042 SANTA TERESA DE VILLA</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-12.18647</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-77.01111</v>
-      </c>
-      <c r="I19" t="n">
-        <v>876</v>
-      </c>
-      <c r="J19" t="n">
-        <v>43</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-12.18647</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-77.01111</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>876</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>7044 SAN MARTIN DE PORRES</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-12.17302</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-77.02318</v>
-      </c>
-      <c r="I20" t="n">
-        <v>653</v>
-      </c>
-      <c r="J20" t="n">
-        <v>33</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-12.17302</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-77.02318</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>653</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>7052 MARIA INMACULADA</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-12.16532</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-77.02388000000001</v>
-      </c>
-      <c r="I21" t="n">
-        <v>663</v>
-      </c>
-      <c r="J21" t="n">
-        <v>26</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-12.16532</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-77.02388</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>663</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>7064 MARIA AUXILIADORA</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-12.18774</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-77.00494</v>
-      </c>
-      <c r="I22" t="n">
-        <v>1884</v>
-      </c>
-      <c r="J22" t="n">
-        <v>80</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-12.18774</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-77.00494</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1884</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>7075 JUAN PABLO II</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-12.1944</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-77.01946</v>
-      </c>
-      <c r="I23" t="n">
-        <v>2097</v>
-      </c>
-      <c r="J23" t="n">
-        <v>97</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-12.1944</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-77.01946</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2097</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1665,20 +1873,30 @@
           <t>7077 LOS REYES ROJOS</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-12.1884</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-77.01949999999999</v>
-      </c>
-      <c r="I24" t="n">
-        <v>861</v>
-      </c>
-      <c r="J24" t="n">
-        <v>39</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-12.1884</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-77.0195</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>861</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1717,20 +1935,30 @@
           <t>7103 PEDRO PAULET Y MOSTAJO</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-12.20491</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-76.97649</v>
-      </c>
-      <c r="I25" t="n">
-        <v>236</v>
-      </c>
-      <c r="J25" t="n">
-        <v>11</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-12.20491</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-76.97649</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1769,20 +1997,30 @@
           <t>BUENOS AIRES DE VILLA</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-12.18745</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-76.99715999999999</v>
-      </c>
-      <c r="I26" t="n">
-        <v>213</v>
-      </c>
-      <c r="J26" t="n">
-        <v>12</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-12.18745</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-76.99716</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1821,20 +2059,30 @@
           <t>LOS ANGELITOS DEL DIVINO NIÑO</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>-12.20061</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-76.98792</v>
-      </c>
-      <c r="I27" t="n">
-        <v>213</v>
-      </c>
-      <c r="J27" t="n">
-        <v>10</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-12.20061</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-76.98792</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1873,20 +2121,30 @@
           <t>COMUNAL SAN JUAN DE LA LIBERTAD</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>-12.19071</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-76.98651</v>
-      </c>
-      <c r="I28" t="n">
-        <v>383</v>
-      </c>
-      <c r="J28" t="n">
-        <v>19</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-12.19071</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-76.98651</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>383</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1925,20 +2183,30 @@
           <t>COMUNAL SANTA ISABEL DE VILLA</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>-12.20091</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-76.97847</v>
-      </c>
-      <c r="I29" t="n">
-        <v>344</v>
-      </c>
-      <c r="J29" t="n">
-        <v>17</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-12.20091</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-76.97847</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>344</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1977,20 +2245,30 @@
           <t>COMUNAL SANTA TERESA</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>-12.18678</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-77.01719</v>
-      </c>
-      <c r="I30" t="n">
-        <v>201</v>
-      </c>
-      <c r="J30" t="n">
-        <v>11</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-12.18678</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-77.01719</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2029,20 +2307,30 @@
           <t>JOSE DE LA RIVA AGUERO Y OSMA</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>-12.16639</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-77.0215</v>
-      </c>
-      <c r="I31" t="n">
-        <v>434</v>
-      </c>
-      <c r="J31" t="n">
-        <v>29</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-12.16639</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-77.0215</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>434</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2081,20 +2369,30 @@
           <t>LOS INKAS</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>-12.20113</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-77.01805</v>
-      </c>
-      <c r="I32" t="n">
-        <v>904</v>
-      </c>
-      <c r="J32" t="n">
-        <v>46</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-12.20113</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-77.01805</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>904</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2133,20 +2431,30 @@
           <t>SAN PEDRO DE CHORRILLOS</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>-12.17363</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-77.0056</v>
-      </c>
-      <c r="I33" t="n">
-        <v>1605</v>
-      </c>
-      <c r="J33" t="n">
-        <v>79</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-12.17363</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-77.0056</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1605</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2185,20 +2493,30 @@
           <t>TUPAC AMARU II</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>-12.19324</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-76.98448999999999</v>
-      </c>
-      <c r="I34" t="n">
-        <v>502</v>
-      </c>
-      <c r="J34" t="n">
-        <v>35</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-12.19324</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-76.98449</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>502</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2237,20 +2555,30 @@
           <t>VIRGEN DEL MORRO SOLAR</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>-12.18604</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-77.0179</v>
-      </c>
-      <c r="I35" t="n">
-        <v>1214</v>
-      </c>
-      <c r="J35" t="n">
-        <v>57</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-12.18604</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-77.0179</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1214</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2289,20 +2617,30 @@
           <t>6053 SAGRADO CORAZON</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>-12.1609</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-77.02361999999999</v>
-      </c>
-      <c r="I36" t="n">
-        <v>773</v>
-      </c>
-      <c r="J36" t="n">
-        <v>37</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-12.1609</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-77.02362</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>773</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2341,20 +2679,30 @@
           <t>CAMBRIDGE COLLEGE LIMA</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>-12.21316</v>
-      </c>
-      <c r="H37" t="n">
-        <v>-77.00384</v>
-      </c>
-      <c r="I37" t="n">
-        <v>1206</v>
-      </c>
-      <c r="J37" t="n">
-        <v>64</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-12.21316</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-77.00384</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1206</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2393,20 +2741,30 @@
           <t>CHRISTIAN BARNARD</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>-12.1963</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-76.9906</v>
-      </c>
-      <c r="I38" t="n">
-        <v>37</v>
-      </c>
-      <c r="J38" t="n">
-        <v>6</v>
-      </c>
-      <c r="K38" t="n">
-        <v>1</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-12.1963</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-76.9906</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2445,20 +2803,30 @@
           <t>CRISTO REDENTOR</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>-12.19323</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-77.01253</v>
-      </c>
-      <c r="I39" t="n">
-        <v>247</v>
-      </c>
-      <c r="J39" t="n">
-        <v>20</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-12.19323</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>-77.01253</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2497,20 +2865,30 @@
           <t>DIVINO MAESTRO</t>
         </is>
       </c>
-      <c r="G40" t="n">
-        <v>-12.20767</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-77.01479999999999</v>
-      </c>
-      <c r="I40" t="n">
-        <v>790</v>
-      </c>
-      <c r="J40" t="n">
-        <v>40</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-12.20767</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-77.0148</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>790</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2549,20 +2927,30 @@
           <t>MARIA REICHE GROSSE NEUMAN</t>
         </is>
       </c>
-      <c r="G41" t="n">
-        <v>-12.19809</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-77.01317</v>
-      </c>
-      <c r="I41" t="n">
-        <v>248</v>
-      </c>
-      <c r="J41" t="n">
-        <v>18</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-12.19809</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-77.01317</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2601,20 +2989,30 @@
           <t>EL HOGAR</t>
         </is>
       </c>
-      <c r="G42" t="n">
-        <v>-12.201</v>
-      </c>
-      <c r="H42" t="n">
-        <v>-76.98905999999999</v>
-      </c>
-      <c r="I42" t="n">
-        <v>271</v>
-      </c>
-      <c r="J42" t="n">
-        <v>16</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-12.201</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>-76.98906</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2653,20 +3051,30 @@
           <t>EL MILAGRO</t>
         </is>
       </c>
-      <c r="G43" t="n">
-        <v>-12.17373</v>
-      </c>
-      <c r="H43" t="n">
-        <v>-77.02355</v>
-      </c>
-      <c r="I43" t="n">
-        <v>203</v>
-      </c>
-      <c r="J43" t="n">
-        <v>19</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-12.17373</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>-77.02355</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -2705,20 +3113,30 @@
           <t>EL SEMBRADOR</t>
         </is>
       </c>
-      <c r="G44" t="n">
-        <v>-12.19528</v>
-      </c>
-      <c r="H44" t="n">
-        <v>-76.99692</v>
-      </c>
-      <c r="I44" t="n">
-        <v>302</v>
-      </c>
-      <c r="J44" t="n">
-        <v>17</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-12.19528</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>-76.99692</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>302</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -2757,20 +3175,30 @@
           <t>LIMA VILLA COLLEGE</t>
         </is>
       </c>
-      <c r="G45" t="n">
-        <v>-12.20706</v>
-      </c>
-      <c r="H45" t="n">
-        <v>-76.99944000000001</v>
-      </c>
-      <c r="I45" t="n">
-        <v>524</v>
-      </c>
-      <c r="J45" t="n">
-        <v>42</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-12.20706</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>-76.99944</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -2809,20 +3237,30 @@
           <t>JESUS MAESTRO</t>
         </is>
       </c>
-      <c r="G46" t="n">
-        <v>-12.1985</v>
-      </c>
-      <c r="H46" t="n">
-        <v>-76.99266</v>
-      </c>
-      <c r="I46" t="n">
-        <v>207</v>
-      </c>
-      <c r="J46" t="n">
-        <v>8</v>
-      </c>
-      <c r="K46" t="n">
-        <v>1</v>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-12.1985</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>-76.99266</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -2861,20 +3299,30 @@
           <t>LA CASA DE CARTON</t>
         </is>
       </c>
-      <c r="G47" t="n">
-        <v>-12.21233</v>
-      </c>
-      <c r="H47" t="n">
-        <v>-77.00935</v>
-      </c>
-      <c r="I47" t="n">
-        <v>268</v>
-      </c>
-      <c r="J47" t="n">
-        <v>31</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-12.21233</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>-77.00935</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -2913,20 +3361,30 @@
           <t>LA ESPERANZA</t>
         </is>
       </c>
-      <c r="G48" t="n">
-        <v>-12.15546</v>
-      </c>
-      <c r="H48" t="n">
-        <v>-77.01873000000001</v>
-      </c>
-      <c r="I48" t="n">
-        <v>233</v>
-      </c>
-      <c r="J48" t="n">
-        <v>15</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-12.15546</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>-77.01873</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -2965,20 +3423,30 @@
           <t>LE D'ALEMBERT</t>
         </is>
       </c>
-      <c r="G49" t="n">
-        <v>-12.18127</v>
-      </c>
-      <c r="H49" t="n">
-        <v>-76.99639999999999</v>
-      </c>
-      <c r="I49" t="n">
-        <v>425</v>
-      </c>
-      <c r="J49" t="n">
-        <v>22</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>-12.18127</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>-76.9964</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>425</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -3017,20 +3485,30 @@
           <t>MARIA DE FATIMA</t>
         </is>
       </c>
-      <c r="G50" t="n">
-        <v>-12.16833</v>
-      </c>
-      <c r="H50" t="n">
-        <v>-77.02406999999999</v>
-      </c>
-      <c r="I50" t="n">
-        <v>46</v>
-      </c>
-      <c r="J50" t="n">
-        <v>4</v>
-      </c>
-      <c r="K50" t="n">
-        <v>2</v>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-12.16833</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>-77.02407</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -3069,20 +3547,30 @@
           <t>MARIA REYNA</t>
         </is>
       </c>
-      <c r="G51" t="n">
-        <v>-12.18753</v>
-      </c>
-      <c r="H51" t="n">
-        <v>-77.00915000000001</v>
-      </c>
-      <c r="I51" t="n">
-        <v>245</v>
-      </c>
-      <c r="J51" t="n">
-        <v>20</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-12.18753</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>-77.00915</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -3121,20 +3609,30 @@
           <t>NIÑO JESUS DE PRAGA</t>
         </is>
       </c>
-      <c r="G52" t="n">
-        <v>-12.16748</v>
-      </c>
-      <c r="H52" t="n">
-        <v>-77.02466</v>
-      </c>
-      <c r="I52" t="n">
-        <v>509</v>
-      </c>
-      <c r="J52" t="n">
-        <v>35</v>
-      </c>
-      <c r="K52" t="n">
-        <v>0</v>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-12.16748</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>-77.02466</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -3173,20 +3671,30 @@
           <t>PEDRO RUIZ GALLO</t>
         </is>
       </c>
-      <c r="G53" t="n">
-        <v>-12.15798</v>
-      </c>
-      <c r="H53" t="n">
-        <v>-77.02294999999999</v>
-      </c>
-      <c r="I53" t="n">
-        <v>2010</v>
-      </c>
-      <c r="J53" t="n">
-        <v>132</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>-12.15798</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>-77.02295</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -3225,20 +3733,30 @@
           <t>SAN AGUSTIN</t>
         </is>
       </c>
-      <c r="G54" t="n">
-        <v>-12.18908</v>
-      </c>
-      <c r="H54" t="n">
-        <v>-77.01401</v>
-      </c>
-      <c r="I54" t="n">
-        <v>140</v>
-      </c>
-      <c r="J54" t="n">
-        <v>9</v>
-      </c>
-      <c r="K54" t="n">
-        <v>1</v>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>-12.18908</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>-77.01401</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -3277,20 +3795,30 @@
           <t>SAN ALFONSO</t>
         </is>
       </c>
-      <c r="G55" t="n">
-        <v>-12.19896</v>
-      </c>
-      <c r="H55" t="n">
-        <v>-77.0027</v>
-      </c>
-      <c r="I55" t="n">
-        <v>248</v>
-      </c>
-      <c r="J55" t="n">
-        <v>13</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0</v>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>-12.19896</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>-77.0027</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -3329,20 +3857,30 @@
           <t>SAN ALFONSO MARIA</t>
         </is>
       </c>
-      <c r="G56" t="n">
-        <v>-12.19916</v>
-      </c>
-      <c r="H56" t="n">
-        <v>-77.00945</v>
-      </c>
-      <c r="I56" t="n">
-        <v>308</v>
-      </c>
-      <c r="J56" t="n">
-        <v>13</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0</v>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>-12.19916</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>-77.00945</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
@@ -3381,20 +3919,30 @@
           <t>SAN LUCAS</t>
         </is>
       </c>
-      <c r="G57" t="n">
-        <v>-12.1687</v>
-      </c>
-      <c r="H57" t="n">
-        <v>-76.99915</v>
-      </c>
-      <c r="I57" t="n">
-        <v>727</v>
-      </c>
-      <c r="J57" t="n">
-        <v>34</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0</v>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>-12.1687</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>-76.99915</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>727</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -3433,20 +3981,30 @@
           <t>SAINT PATRICK'S CHILDREN</t>
         </is>
       </c>
-      <c r="G58" t="n">
-        <v>-12.17846</v>
-      </c>
-      <c r="H58" t="n">
-        <v>-77.01406</v>
-      </c>
-      <c r="I58" t="n">
-        <v>72</v>
-      </c>
-      <c r="J58" t="n">
-        <v>5</v>
-      </c>
-      <c r="K58" t="n">
-        <v>1</v>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>-12.17846</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>-77.01406</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -3485,20 +4043,30 @@
           <t>SANTISIMA MARIA</t>
         </is>
       </c>
-      <c r="G59" t="n">
-        <v>-12.19967</v>
-      </c>
-      <c r="H59" t="n">
-        <v>-77.00699</v>
-      </c>
-      <c r="I59" t="n">
-        <v>307</v>
-      </c>
-      <c r="J59" t="n">
-        <v>18</v>
-      </c>
-      <c r="K59" t="n">
-        <v>0</v>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>-12.19967</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>-77.00699</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
@@ -3537,20 +4105,30 @@
           <t>SANTISIMA TRINIDAD</t>
         </is>
       </c>
-      <c r="G60" t="n">
-        <v>-12.19227</v>
-      </c>
-      <c r="H60" t="n">
-        <v>-77.01918999999999</v>
-      </c>
-      <c r="I60" t="n">
-        <v>69</v>
-      </c>
-      <c r="J60" t="n">
-        <v>10</v>
-      </c>
-      <c r="K60" t="n">
-        <v>1</v>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>-12.19227</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>-77.01919</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -3589,20 +4167,30 @@
           <t>SEÑOR DE LUREN</t>
         </is>
       </c>
-      <c r="G61" t="n">
-        <v>-12.19287</v>
-      </c>
-      <c r="H61" t="n">
-        <v>-76.98384</v>
-      </c>
-      <c r="I61" t="n">
-        <v>245</v>
-      </c>
-      <c r="J61" t="n">
-        <v>16</v>
-      </c>
-      <c r="K61" t="n">
-        <v>0</v>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>-12.19287</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>-76.98384</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
@@ -3641,20 +4229,30 @@
           <t>ASOCIACION EDUCATIVA VIRGEN DE LA FAMILIA</t>
         </is>
       </c>
-      <c r="G62" t="n">
-        <v>-12.17369</v>
-      </c>
-      <c r="H62" t="n">
-        <v>-77.02415999999999</v>
-      </c>
-      <c r="I62" t="n">
-        <v>260</v>
-      </c>
-      <c r="J62" t="n">
-        <v>20</v>
-      </c>
-      <c r="K62" t="n">
-        <v>0</v>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>-12.17369</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>-77.02416</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
@@ -3693,20 +4291,30 @@
           <t>FE Y ALEGRIA 34</t>
         </is>
       </c>
-      <c r="G63" t="n">
-        <v>-12.19328</v>
-      </c>
-      <c r="H63" t="n">
-        <v>-76.98985</v>
-      </c>
-      <c r="I63" t="n">
-        <v>1081</v>
-      </c>
-      <c r="J63" t="n">
-        <v>55</v>
-      </c>
-      <c r="K63" t="n">
-        <v>0</v>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>-12.19328</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>-76.98985</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
@@ -3745,20 +4353,30 @@
           <t>VILLA ALARIFE</t>
         </is>
       </c>
-      <c r="G64" t="n">
-        <v>-12.20821</v>
-      </c>
-      <c r="H64" t="n">
-        <v>-77.00462</v>
-      </c>
-      <c r="I64" t="n">
-        <v>537</v>
-      </c>
-      <c r="J64" t="n">
-        <v>59</v>
-      </c>
-      <c r="K64" t="n">
-        <v>0</v>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>-12.20821</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>-77.00462</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>537</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
@@ -3797,20 +4415,30 @@
           <t>SAINT PATRICK'S SCHOOL</t>
         </is>
       </c>
-      <c r="G65" t="n">
-        <v>-12.18088</v>
-      </c>
-      <c r="H65" t="n">
-        <v>-77.01103000000001</v>
-      </c>
-      <c r="I65" t="n">
-        <v>455</v>
-      </c>
-      <c r="J65" t="n">
-        <v>24</v>
-      </c>
-      <c r="K65" t="n">
-        <v>0</v>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>-12.18088</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>-77.01103</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
@@ -3849,20 +4477,30 @@
           <t>PALAS ATENEA</t>
         </is>
       </c>
-      <c r="G66" t="n">
-        <v>-12.16998</v>
-      </c>
-      <c r="H66" t="n">
-        <v>-76.99534</v>
-      </c>
-      <c r="I66" t="n">
-        <v>754</v>
-      </c>
-      <c r="J66" t="n">
-        <v>43</v>
-      </c>
-      <c r="K66" t="n">
-        <v>0</v>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>-12.16998</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>-76.99534</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>754</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -3901,20 +4539,30 @@
           <t>PROLOG DE CHORRILLOS</t>
         </is>
       </c>
-      <c r="G67" t="n">
-        <v>-12.20551</v>
-      </c>
-      <c r="H67" t="n">
-        <v>-77.0171</v>
-      </c>
-      <c r="I67" t="n">
-        <v>248</v>
-      </c>
-      <c r="J67" t="n">
-        <v>27</v>
-      </c>
-      <c r="K67" t="n">
-        <v>0</v>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>-12.20551</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>-77.0171</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
@@ -3953,20 +4601,30 @@
           <t>CORONEL JOSE JOAQUIN INCLAN</t>
         </is>
       </c>
-      <c r="G68" t="n">
-        <v>-12.17147</v>
-      </c>
-      <c r="H68" t="n">
-        <v>-77.01034</v>
-      </c>
-      <c r="I68" t="n">
-        <v>1104</v>
-      </c>
-      <c r="J68" t="n">
-        <v>40</v>
-      </c>
-      <c r="K68" t="n">
-        <v>0</v>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>-12.17147</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>-77.01034</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1104</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
@@ -4005,20 +4663,30 @@
           <t>MILAGRITOS DE JESUS</t>
         </is>
       </c>
-      <c r="G69" t="n">
-        <v>-12.19937</v>
-      </c>
-      <c r="H69" t="n">
-        <v>-76.97898000000001</v>
-      </c>
-      <c r="I69" t="n">
-        <v>381</v>
-      </c>
-      <c r="J69" t="n">
-        <v>18</v>
-      </c>
-      <c r="K69" t="n">
-        <v>0</v>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>-12.19937</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>-76.97898</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>381</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
@@ -4057,20 +4725,30 @@
           <t>6086 SANTA ISABEL</t>
         </is>
       </c>
-      <c r="G70" t="n">
-        <v>-12.20096</v>
-      </c>
-      <c r="H70" t="n">
-        <v>-76.97749</v>
-      </c>
-      <c r="I70" t="n">
-        <v>1496</v>
-      </c>
-      <c r="J70" t="n">
-        <v>70</v>
-      </c>
-      <c r="K70" t="n">
-        <v>0</v>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>-12.20096</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>-76.97749</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1496</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
@@ -4109,20 +4787,30 @@
           <t>6097 MATEO PUMACAHUA</t>
         </is>
       </c>
-      <c r="G71" t="n">
-        <v>-12.19209</v>
-      </c>
-      <c r="H71" t="n">
-        <v>-76.98049</v>
-      </c>
-      <c r="I71" t="n">
-        <v>2010</v>
-      </c>
-      <c r="J71" t="n">
-        <v>94</v>
-      </c>
-      <c r="K71" t="n">
-        <v>0</v>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>-12.19209</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>-76.98049</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
@@ -4161,20 +4849,30 @@
           <t>7076 LAS BRISAS DE VILLA</t>
         </is>
       </c>
-      <c r="G72" t="n">
-        <v>-12.1973</v>
-      </c>
-      <c r="H72" t="n">
-        <v>-76.97490000000001</v>
-      </c>
-      <c r="I72" t="n">
-        <v>2066</v>
-      </c>
-      <c r="J72" t="n">
-        <v>89</v>
-      </c>
-      <c r="K72" t="n">
-        <v>0</v>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>-12.1973</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>-76.9749</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>2066</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
@@ -4213,20 +4911,30 @@
           <t>YACHAYHUASI</t>
         </is>
       </c>
-      <c r="G73" t="n">
-        <v>-12.20267</v>
-      </c>
-      <c r="H73" t="n">
-        <v>-76.97806</v>
-      </c>
-      <c r="I73" t="n">
-        <v>252</v>
-      </c>
-      <c r="J73" t="n">
-        <v>18</v>
-      </c>
-      <c r="K73" t="n">
-        <v>0</v>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>-12.20267</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>-76.97806</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
@@ -4265,20 +4973,30 @@
           <t>7707 CRISTO REY</t>
         </is>
       </c>
-      <c r="G74" t="n">
-        <v>-12.16906</v>
-      </c>
-      <c r="H74" t="n">
-        <v>-77.02996</v>
-      </c>
-      <c r="I74" t="n">
-        <v>461</v>
-      </c>
-      <c r="J74" t="n">
-        <v>33</v>
-      </c>
-      <c r="K74" t="n">
-        <v>0</v>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>-12.16906</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>-77.02996</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>461</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
@@ -4317,20 +5035,30 @@
           <t>CAPULLITOS DE JESUS</t>
         </is>
       </c>
-      <c r="G75" t="n">
-        <v>-12.1957</v>
-      </c>
-      <c r="H75" t="n">
-        <v>-77.02095</v>
-      </c>
-      <c r="I75" t="n">
-        <v>302</v>
-      </c>
-      <c r="J75" t="n">
-        <v>15</v>
-      </c>
-      <c r="K75" t="n">
-        <v>0</v>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>-12.1957</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-77.02095</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>302</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
@@ -4369,20 +5097,30 @@
           <t>LOS INGENIEROS DE MATELLINI</t>
         </is>
       </c>
-      <c r="G76" t="n">
-        <v>-12.1745</v>
-      </c>
-      <c r="H76" t="n">
-        <v>-77.00303</v>
-      </c>
-      <c r="I76" t="n">
-        <v>292</v>
-      </c>
-      <c r="J76" t="n">
-        <v>15</v>
-      </c>
-      <c r="K76" t="n">
-        <v>0</v>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>-12.1745</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>-77.00303</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>292</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
@@ -4421,20 +5159,30 @@
           <t>LEONARD EULER CHORRILLOS</t>
         </is>
       </c>
-      <c r="G77" t="n">
-        <v>-12.173963</v>
-      </c>
-      <c r="H77" t="n">
-        <v>-76.99476</v>
-      </c>
-      <c r="I77" t="n">
-        <v>597</v>
-      </c>
-      <c r="J77" t="n">
-        <v>24</v>
-      </c>
-      <c r="K77" t="n">
-        <v>0</v>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>-12.173963</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>-76.99476</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>597</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
@@ -4473,20 +5221,30 @@
           <t>INNOVA SCHOOLS - CHORRILLOS VILLA</t>
         </is>
       </c>
-      <c r="G78" t="n">
-        <v>-12.20657</v>
-      </c>
-      <c r="H78" t="n">
-        <v>-77.00792</v>
-      </c>
-      <c r="I78" t="n">
-        <v>967</v>
-      </c>
-      <c r="J78" t="n">
-        <v>44</v>
-      </c>
-      <c r="K78" t="n">
-        <v>0</v>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>-12.20657</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>-77.00792</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>967</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
@@ -4525,20 +5283,30 @@
           <t>LICEO NAVAL CAPITAN DE NAVIO JUAN FANNING GARCIA</t>
         </is>
       </c>
-      <c r="G79" t="n">
-        <v>-12.19497</v>
-      </c>
-      <c r="H79" t="n">
-        <v>-76.9892</v>
-      </c>
-      <c r="I79" t="n">
-        <v>500</v>
-      </c>
-      <c r="J79" t="n">
-        <v>41</v>
-      </c>
-      <c r="K79" t="n">
-        <v>0</v>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>-12.19497</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>-76.9892</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
@@ -4577,20 +5345,30 @@
           <t>INNOVA SCHOOLS - CHORRILLOS FAISANES</t>
         </is>
       </c>
-      <c r="G80" t="n">
-        <v>-12.17101</v>
-      </c>
-      <c r="H80" t="n">
-        <v>-76.99362000000001</v>
-      </c>
-      <c r="I80" t="n">
-        <v>1041</v>
-      </c>
-      <c r="J80" t="n">
-        <v>52</v>
-      </c>
-      <c r="K80" t="n">
-        <v>0</v>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>-12.17101</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>-76.99362</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>1041</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
@@ -4629,20 +5407,30 @@
           <t>ST. GEORGE'S COLLEGE II</t>
         </is>
       </c>
-      <c r="G81" t="n">
-        <v>-12.20957</v>
-      </c>
-      <c r="H81" t="n">
-        <v>-77.00218</v>
-      </c>
-      <c r="I81" t="n">
-        <v>1021</v>
-      </c>
-      <c r="J81" t="n">
-        <v>67</v>
-      </c>
-      <c r="K81" t="n">
-        <v>0</v>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>-12.20957</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>-77.00218</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>1021</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
@@ -4681,20 +5469,30 @@
           <t>SANTO DOMINGO</t>
         </is>
       </c>
-      <c r="G82" t="n">
-        <v>-12.205</v>
-      </c>
-      <c r="H82" t="n">
-        <v>-77.01139000000001</v>
-      </c>
-      <c r="I82" t="n">
-        <v>823</v>
-      </c>
-      <c r="J82" t="n">
-        <v>37</v>
-      </c>
-      <c r="K82" t="n">
-        <v>0</v>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>-12.205</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>-77.01139</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>823</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
@@ -4733,20 +5531,30 @@
           <t>ISABEL FLORES DE OLIVA</t>
         </is>
       </c>
-      <c r="G83" t="n">
-        <v>-12.18295</v>
-      </c>
-      <c r="H83" t="n">
-        <v>-76.99897</v>
-      </c>
-      <c r="I83" t="n">
-        <v>137</v>
-      </c>
-      <c r="J83" t="n">
-        <v>23</v>
-      </c>
-      <c r="K83" t="n">
-        <v>1</v>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>-12.18295</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>-76.99897</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
@@ -4785,20 +5593,30 @@
           <t>MAHATMA GANDHI</t>
         </is>
       </c>
-      <c r="G84" t="n">
-        <v>-12.20215</v>
-      </c>
-      <c r="H84" t="n">
-        <v>-76.97750000000001</v>
-      </c>
-      <c r="I84" t="n">
-        <v>231</v>
-      </c>
-      <c r="J84" t="n">
-        <v>14</v>
-      </c>
-      <c r="K84" t="n">
-        <v>0</v>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>-12.20215</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>-76.9775</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
@@ -4837,20 +5655,30 @@
           <t>MARIANO SANTOS MATEO</t>
         </is>
       </c>
-      <c r="G85" t="n">
-        <v>-12.19742</v>
-      </c>
-      <c r="H85" t="n">
-        <v>-77.02392</v>
-      </c>
-      <c r="I85" t="n">
-        <v>185</v>
-      </c>
-      <c r="J85" t="n">
-        <v>21</v>
-      </c>
-      <c r="K85" t="n">
-        <v>1</v>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>-12.19742</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>-77.02392</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
@@ -4889,20 +5717,30 @@
           <t>SANTO DOMINGO</t>
         </is>
       </c>
-      <c r="G86" t="n">
-        <v>-12.20484</v>
-      </c>
-      <c r="H86" t="n">
-        <v>-77.01099000000001</v>
-      </c>
-      <c r="I86" t="n">
-        <v>738</v>
-      </c>
-      <c r="J86" t="n">
-        <v>37</v>
-      </c>
-      <c r="K86" t="n">
-        <v>0</v>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>-12.20484</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>-77.01099</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>738</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
@@ -4941,20 +5779,30 @@
           <t>DE COLORES</t>
         </is>
       </c>
-      <c r="G87" t="n">
-        <v>-12.17403</v>
-      </c>
-      <c r="H87" t="n">
-        <v>-77.0213</v>
-      </c>
-      <c r="I87" t="n">
-        <v>242</v>
-      </c>
-      <c r="J87" t="n">
-        <v>13</v>
-      </c>
-      <c r="K87" t="n">
-        <v>0</v>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>-12.17403</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>-77.0213</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
@@ -4993,20 +5841,30 @@
           <t>BELEN</t>
         </is>
       </c>
-      <c r="G88" t="n">
-        <v>-12.17445</v>
-      </c>
-      <c r="H88" t="n">
-        <v>-76.99914</v>
-      </c>
-      <c r="I88" t="n">
-        <v>418</v>
-      </c>
-      <c r="J88" t="n">
-        <v>26</v>
-      </c>
-      <c r="K88" t="n">
-        <v>0</v>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>-12.17445</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>-76.99914</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>418</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
@@ -5045,20 +5903,30 @@
           <t>ARQUITECTO FERNANDO BELAUNDE TERRY</t>
         </is>
       </c>
-      <c r="G89" t="n">
-        <v>-12.20464</v>
-      </c>
-      <c r="H89" t="n">
-        <v>-77.01626</v>
-      </c>
-      <c r="I89" t="n">
-        <v>635</v>
-      </c>
-      <c r="J89" t="n">
-        <v>27</v>
-      </c>
-      <c r="K89" t="n">
-        <v>0</v>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>-12.20464</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>-77.01626</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>635</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
@@ -5097,20 +5965,30 @@
           <t>SEMILLITAS DEL FUTURO</t>
         </is>
       </c>
-      <c r="G90" t="n">
-        <v>-12.18766</v>
-      </c>
-      <c r="H90" t="n">
-        <v>-76.99101</v>
-      </c>
-      <c r="I90" t="n">
-        <v>69</v>
-      </c>
-      <c r="J90" t="n">
-        <v>6</v>
-      </c>
-      <c r="K90" t="n">
-        <v>1</v>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>-12.18766</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>-76.99101</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
@@ -5149,20 +6027,30 @@
           <t>ALEPH</t>
         </is>
       </c>
-      <c r="G91" t="n">
-        <v>-12.20034</v>
-      </c>
-      <c r="H91" t="n">
-        <v>-77.0001</v>
-      </c>
-      <c r="I91" t="n">
-        <v>847</v>
-      </c>
-      <c r="J91" t="n">
-        <v>31</v>
-      </c>
-      <c r="K91" t="n">
-        <v>0</v>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>-12.20034</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>-77.0001</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>847</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
@@ -5201,20 +6089,30 @@
           <t>SEMILLITAS DE BUENOS AIRES DE VILLA</t>
         </is>
       </c>
-      <c r="G92" t="n">
-        <v>-12.18662</v>
-      </c>
-      <c r="H92" t="n">
-        <v>-76.99692</v>
-      </c>
-      <c r="I92" t="n">
-        <v>29</v>
-      </c>
-      <c r="J92" t="n">
-        <v>4</v>
-      </c>
-      <c r="K92" t="n">
-        <v>1</v>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>-12.18662</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>-76.99692</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
@@ -5253,20 +6151,30 @@
           <t>INNOVA SCHOOLS - CHORRILLOS LA CAMPIÑA</t>
         </is>
       </c>
-      <c r="G93" t="n">
-        <v>-12.17812</v>
-      </c>
-      <c r="H93" t="n">
-        <v>-77.00345</v>
-      </c>
-      <c r="I93" t="n">
-        <v>979</v>
-      </c>
-      <c r="J93" t="n">
-        <v>45</v>
-      </c>
-      <c r="K93" t="n">
-        <v>0</v>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>-12.17812</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>-77.00345</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>979</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
@@ -5305,20 +6213,30 @@
           <t>DIVINO MAESTRO LOS CEDROS</t>
         </is>
       </c>
-      <c r="G94" t="n">
-        <v>-12.20618</v>
-      </c>
-      <c r="H94" t="n">
-        <v>-77.01379</v>
-      </c>
-      <c r="I94" t="n">
-        <v>299</v>
-      </c>
-      <c r="J94" t="n">
-        <v>17</v>
-      </c>
-      <c r="K94" t="n">
-        <v>0</v>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>-12.20618</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>-77.01379</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
@@ -5357,20 +6275,30 @@
           <t>THOMAS ALVA EDISON</t>
         </is>
       </c>
-      <c r="G95" t="n">
-        <v>-12.20342</v>
-      </c>
-      <c r="H95" t="n">
-        <v>-76.97492</v>
-      </c>
-      <c r="I95" t="n">
-        <v>376</v>
-      </c>
-      <c r="J95" t="n">
-        <v>25</v>
-      </c>
-      <c r="K95" t="n">
-        <v>0</v>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>-12.20342</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>-76.97492</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>376</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
@@ -5409,20 +6337,30 @@
           <t>INNOVA SCHOOLS - CHORRILLOS UNIVERSO 2</t>
         </is>
       </c>
-      <c r="G96" t="n">
-        <v>-12.17266</v>
-      </c>
-      <c r="H96" t="n">
-        <v>-76.99717</v>
-      </c>
-      <c r="I96" t="n">
-        <v>551</v>
-      </c>
-      <c r="J96" t="n">
-        <v>29</v>
-      </c>
-      <c r="K96" t="n">
-        <v>0</v>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>-12.17266</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>-76.99717</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>551</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
@@ -5461,20 +6399,30 @@
           <t>INNOVA SCHOOLS - CHORRILLOS UNIVERSO 1</t>
         </is>
       </c>
-      <c r="G97" t="n">
-        <v>-12.17103</v>
-      </c>
-      <c r="H97" t="n">
-        <v>-76.99497</v>
-      </c>
-      <c r="I97" t="n">
-        <v>370</v>
-      </c>
-      <c r="J97" t="n">
-        <v>23</v>
-      </c>
-      <c r="K97" t="n">
-        <v>0</v>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>-12.17103</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>-76.99497</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
@@ -5513,20 +6461,30 @@
           <t>TRILCE CHORRILLOS</t>
         </is>
       </c>
-      <c r="G98" t="n">
-        <v>-12.20468</v>
-      </c>
-      <c r="H98" t="n">
-        <v>-77.00758</v>
-      </c>
-      <c r="I98" t="n">
-        <v>825</v>
-      </c>
-      <c r="J98" t="n">
-        <v>27</v>
-      </c>
-      <c r="K98" t="n">
-        <v>0</v>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>-12.20468</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>-77.00758</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>825</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
@@ -5565,20 +6523,30 @@
           <t>GRACIAS JESUS</t>
         </is>
       </c>
-      <c r="G99" t="n">
-        <v>-12.17083</v>
-      </c>
-      <c r="H99" t="n">
-        <v>-77.00035</v>
-      </c>
-      <c r="I99" t="n">
-        <v>217</v>
-      </c>
-      <c r="J99" t="n">
-        <v>10</v>
-      </c>
-      <c r="K99" t="n">
-        <v>0</v>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>-12.17083</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>-77.00035</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
@@ -5617,20 +6585,30 @@
           <t>SANTISIMA MARIA</t>
         </is>
       </c>
-      <c r="G100" t="n">
-        <v>-12.19957</v>
-      </c>
-      <c r="H100" t="n">
-        <v>-77.00713</v>
-      </c>
-      <c r="I100" t="n">
-        <v>332</v>
-      </c>
-      <c r="J100" t="n">
-        <v>18</v>
-      </c>
-      <c r="K100" t="n">
-        <v>0</v>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>-12.19957</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>-77.00713</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
@@ -5669,20 +6647,30 @@
           <t>SACO OLIVEROS DE SANTA ISABEL</t>
         </is>
       </c>
-      <c r="G101" t="n">
-        <v>-12.17109</v>
-      </c>
-      <c r="H101" t="n">
-        <v>-76.99497</v>
-      </c>
-      <c r="I101" t="n">
-        <v>1240</v>
-      </c>
-      <c r="J101" t="n">
-        <v>40</v>
-      </c>
-      <c r="K101" t="n">
-        <v>0</v>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>-12.17109</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>-76.99497</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>1240</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
@@ -5721,20 +6709,30 @@
           <t>7037 ARIOSTO MATELLINI ESPINOZA</t>
         </is>
       </c>
-      <c r="G102" t="n">
-        <v>-12.16736</v>
-      </c>
-      <c r="H102" t="n">
-        <v>-76.99965</v>
-      </c>
-      <c r="I102" t="n">
-        <v>704</v>
-      </c>
-      <c r="J102" t="n">
-        <v>31</v>
-      </c>
-      <c r="K102" t="n">
-        <v>0</v>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>-12.16736</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>-76.99965</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>704</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
@@ -5773,20 +6771,30 @@
           <t>YACHAYHUASI</t>
         </is>
       </c>
-      <c r="G103" t="n">
-        <v>-12.20389</v>
-      </c>
-      <c r="H103" t="n">
-        <v>-76.97946</v>
-      </c>
-      <c r="I103" t="n">
-        <v>272</v>
-      </c>
-      <c r="J103" t="n">
-        <v>17</v>
-      </c>
-      <c r="K103" t="n">
-        <v>0</v>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>-12.20389</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>-76.97946</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
@@ -5825,20 +6833,30 @@
           <t>LOS INGENIEROS DE SAN MARCOS</t>
         </is>
       </c>
-      <c r="G104" t="n">
-        <v>-12.195404</v>
-      </c>
-      <c r="H104" t="n">
-        <v>-77.013195</v>
-      </c>
-      <c r="I104" t="n">
-        <v>306</v>
-      </c>
-      <c r="J104" t="n">
-        <v>19</v>
-      </c>
-      <c r="K104" t="n">
-        <v>0</v>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>-12.195404</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>-77.013195</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
@@ -5877,20 +6895,30 @@
           <t>PROLOG DE DELICIAS</t>
         </is>
       </c>
-      <c r="G105" t="n">
-        <v>-12.198064</v>
-      </c>
-      <c r="H105" t="n">
-        <v>-76.98633</v>
-      </c>
-      <c r="I105" t="n">
-        <v>617</v>
-      </c>
-      <c r="J105" t="n">
-        <v>53</v>
-      </c>
-      <c r="K105" t="n">
-        <v>0</v>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>-12.198064</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>-76.98633</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
@@ -5929,20 +6957,30 @@
           <t>MASTER SCHOOL CHORRILLOS</t>
         </is>
       </c>
-      <c r="G106" t="n">
-        <v>-12.19643</v>
-      </c>
-      <c r="H106" t="n">
-        <v>-76.99082</v>
-      </c>
-      <c r="I106" t="n">
-        <v>46</v>
-      </c>
-      <c r="J106" t="n">
-        <v>4</v>
-      </c>
-      <c r="K106" t="n">
-        <v>1</v>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>-12.19643</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>-76.99082</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/LIMA-LIMA-CHORRILLOS.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-CHORRILLOS.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>298623</t>
+          <t>298963</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>518 LOS ANGELES DE JESUS</t>
+          <t>LOS ANGELITOS DEL DIVINO NIÑO</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-12.17658</t>
+          <t>-12.20061</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-77.0094</t>
+          <t>-76.98792</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>213</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,37 +563,37 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>298637</t>
+          <t>300112</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>VIRGEN MARIA MADRE DE LOS NIÑOS</t>
+          <t>SANTISIMA TRINIDAD</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-12.19044</t>
+          <t>-12.19227</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-77.01063</t>
+          <t>-77.01919</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>69</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>298722</t>
+          <t>836397</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>59 SANTA LUCIA</t>
+          <t>GRACIAS JESUS</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-12.16549</t>
+          <t>-12.17083</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-77.02537</t>
+          <t>-77.00035</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>446</t>
+          <t>217</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>298736</t>
+          <t>298944</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>6005 GENERAL EMILIO SOYER CABERO</t>
+          <t>7103 PEDRO PAULET Y MOSTAJO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-12.16355</t>
+          <t>-12.20491</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-77.02045</t>
+          <t>-76.97649</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>236</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>298741</t>
+          <t>298996</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>7066 ANDRES AVELINO CACERES</t>
+          <t>COMUNAL SANTA TERESA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-12.19998</t>
+          <t>-12.18678</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-76.99325</t>
+          <t>-77.01719</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>201</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>298760</t>
+          <t>298784</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>6075 JOSE MARIA ARGUEDAS</t>
+          <t>6090 JOSE OLAYA BALANDRA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-12.19814</t>
+          <t>-12.19442</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-76.98143</t>
+          <t>-77.0063</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>2685</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>113</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>298779</t>
+          <t>298958</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>6085 BRIGIDA SILVA DE OCHOA</t>
+          <t>BUENOS AIRES DE VILLA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-12.164653</t>
+          <t>-12.18745</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-77.020892</t>
+          <t>-76.99716</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1238</t>
+          <t>213</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>298784</t>
+          <t>298623</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>6090 JOSE OLAYA BALANDRA</t>
+          <t>518 LOS ANGELES DE JESUS</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-12.19442</t>
+          <t>-12.17658</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-77.0063</t>
+          <t>-77.0094</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2685</t>
+          <t>278</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>298798</t>
+          <t>299892</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>6091 CESAR VALLEJO</t>
+          <t>SAN ALFONSO</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-12.18918</t>
+          <t>-12.19896</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-76.99095</t>
+          <t>-77.0027</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1470</t>
+          <t>248</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>298802</t>
+          <t>299910</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>6092 LOS REYES CATOLICOS</t>
+          <t>SAN ALFONSO MARIA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-12.18701</t>
+          <t>-12.19916</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-77.01684</t>
+          <t>-77.00945</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>871</t>
+          <t>308</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>298816</t>
+          <t>725016</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>6094 SANTA ROSA</t>
+          <t>DE COLORES</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-12.19016</t>
+          <t>-12.17403</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-77.01041</t>
+          <t>-77.0213</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1539</t>
+          <t>242</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>298821</t>
+          <t>299849</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>6153 CAPITAN DEL EJERCITO PERUANO AUGUSTO JAVIER GUTIERREZ MENDOZA</t>
+          <t>PEDRO RUIZ GALLO</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-12.1904</t>
+          <t>-12.15798</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-76.9869</t>
+          <t>-77.02295</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>132</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>298835</t>
+          <t>723833</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>7034 ENRIQUE NERINI COLLAZOS</t>
+          <t>MAHATMA GANDHI</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-12.17172</t>
+          <t>-12.20215</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-77.024447</t>
+          <t>-76.9775</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>849</t>
+          <t>231</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>298840</t>
+          <t>299533</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>7036 ANGELICA RECHARTE CORRALES</t>
+          <t>LA ESPERANZA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-12.16583</t>
+          <t>-12.15546</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-77.02445</t>
+          <t>-77.01873</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>233</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>298859</t>
+          <t>537708</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>7037 ARIOSTO MATELLINI ESPINOZA</t>
+          <t>CAPULLITOS DE JESUS</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-12.16701</t>
+          <t>-12.1957</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-76.99938</t>
+          <t>-77.02095</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>302</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>298864</t>
+          <t>572711</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>7038 CORAZON DE JESUS DE ARMATAMBO</t>
+          <t>LOS INGENIEROS DE MATELLINI</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-12.1789</t>
+          <t>-12.1745</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-77.02239</t>
+          <t>-77.00303</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1067</t>
+          <t>292</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>298878</t>
+          <t>299340</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>7039 MANUEL SCORZA TORRES</t>
+          <t>EL HOGAR</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-12.18322</t>
+          <t>-12.201</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-76.9927</t>
+          <t>-76.98906</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1372</t>
+          <t>271</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>298883</t>
+          <t>300150</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>7042 SANTA TERESA DE VILLA</t>
+          <t>SEÑOR DE LUREN</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-12.18647</t>
+          <t>-12.19287</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-77.01111</t>
+          <t>-76.98384</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>245</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>298897</t>
+          <t>298982</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>7044 SAN MARTIN DE PORRES</t>
+          <t>COMUNAL SANTA ISABEL DE VILLA</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-12.17302</t>
+          <t>-12.20091</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-77.02318</t>
+          <t>-76.97847</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>344</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>298901</t>
+          <t>299364</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>7052 MARIA INMACULADA</t>
+          <t>EL SEMBRADOR</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-12.16532</t>
+          <t>-12.19528</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-77.02388</t>
+          <t>-76.99692</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>302</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>298915</t>
+          <t>780654</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>7064 MARIA AUXILIADORA</t>
+          <t>DIVINO MAESTRO LOS CEDROS</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-12.18774</t>
+          <t>-12.20618</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-77.00494</t>
+          <t>-77.01379</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1884</t>
+          <t>299</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>298920</t>
+          <t>858365</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>7075 JUAN PABLO II</t>
+          <t>YACHAYHUASI</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-12.1944</t>
+          <t>-12.20389</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-77.01946</t>
+          <t>-76.97946</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2097</t>
+          <t>272</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>298939</t>
+          <t>298637</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>7077 LOS REYES ROJOS</t>
+          <t>VIRGEN MARIA MADRE DE LOS NIÑOS</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-12.1884</t>
+          <t>-12.19044</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-77.0195</t>
+          <t>-77.01063</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>410</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>298944</t>
+          <t>299335</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>7103 PEDRO PAULET Y MOSTAJO</t>
+          <t>MARIA REICHE GROSSE NEUMAN</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-12.20491</t>
+          <t>-12.19809</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-76.97649</t>
+          <t>-77.01317</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>248</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>298958</t>
+          <t>300107</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>BUENOS AIRES DE VILLA</t>
+          <t>SANTISIMA MARIA</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-12.18745</t>
+          <t>-12.19967</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-76.99716</t>
+          <t>-77.00699</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>307</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>298963</t>
+          <t>340090</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>LOS ANGELITOS DEL DIVINO NIÑO</t>
+          <t>MILAGRITOS DE JESUS</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-12.20061</t>
+          <t>-12.19937</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-76.98792</t>
+          <t>-76.97898</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>381</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>298977</t>
+          <t>342032</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>COMUNAL SAN JUAN DE LA LIBERTAD</t>
+          <t>YACHAYHUASI</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-12.19071</t>
+          <t>-12.20267</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-76.98651</t>
+          <t>-76.97806</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>252</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>298982</t>
+          <t>843411</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>COMUNAL SANTA ISABEL DE VILLA</t>
+          <t>SANTISIMA MARIA</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-12.20091</t>
+          <t>-12.19957</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-76.97847</t>
+          <t>-77.00713</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>344</t>
+          <t>332</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>298996</t>
+          <t>298977</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>COMUNAL SANTA TERESA</t>
+          <t>COMUNAL SAN JUAN DE LA LIBERTAD</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-12.18678</t>
+          <t>-12.19071</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-77.01719</t>
+          <t>-76.98651</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>383</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>299024</t>
+          <t>299359</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>JOSE DE LA RIVA AGUERO Y OSMA</t>
+          <t>EL MILAGRO</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-12.16639</t>
+          <t>-12.17373</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-77.0215</t>
+          <t>-77.02355</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>434</t>
+          <t>203</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>299043</t>
+          <t>904287</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>LOS INKAS</t>
+          <t>LOS INGENIEROS DE SAN MARCOS</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-12.20113</t>
+          <t>-12.195404</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-77.01805</t>
+          <t>-77.013195</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>904</t>
+          <t>306</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>299062</t>
+          <t>299284</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>SAN PEDRO DE CHORRILLOS</t>
+          <t>CRISTO REDENTOR</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-12.17363</t>
+          <t>-12.19323</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-77.0056</t>
+          <t>-77.01253</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1605</t>
+          <t>247</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>299076</t>
+          <t>299665</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>TUPAC AMARU II</t>
+          <t>MARIA REYNA</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-12.19324</t>
+          <t>-12.18753</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-76.98449</t>
+          <t>-77.00915</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>502</t>
+          <t>245</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>299081</t>
+          <t>300225</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>VIRGEN DEL MORRO SOLAR</t>
+          <t>ASOCIACION EDUCATIVA VIRGEN DE LA FAMILIA</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-12.18604</t>
+          <t>-12.17369</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-77.0179</t>
+          <t>-77.02416</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1214</t>
+          <t>260</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,37 +2609,37 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>299118</t>
+          <t>724253</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>6053 SAGRADO CORAZON</t>
+          <t>MARIANO SANTOS MATEO</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-12.1609</t>
+          <t>-12.19742</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-77.02362</t>
+          <t>-77.02392</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>773</t>
+          <t>185</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>299199</t>
+          <t>299552</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>CAMBRIDGE COLLEGE LIMA</t>
+          <t>LE D'ALEMBERT</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-12.21316</t>
+          <t>-12.18127</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-77.00384</t>
+          <t>-76.9964</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1206</t>
+          <t>425</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>299222</t>
+          <t>723729</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>CHRISTIAN BARNARD</t>
+          <t>ISABEL FLORES DE OLIVA</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-12.1963</t>
+          <t>-12.18295</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-76.9906</t>
+          <t>-76.99897</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>137</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>299284</t>
+          <t>831093</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>CRISTO REDENTOR</t>
+          <t>INNOVA SCHOOLS - CHORRILLOS UNIVERSO 1</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-12.19323</t>
+          <t>-12.17103</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-77.01253</t>
+          <t>-76.99497</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>370</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>299302</t>
+          <t>300517</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>DIVINO MAESTRO</t>
+          <t>SAINT PATRICK'S SCHOOL</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-12.20767</t>
+          <t>-12.18088</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-77.0148</t>
+          <t>-77.01103</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>790</t>
+          <t>455</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>299335</t>
+          <t>582159</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>MARIA REICHE GROSSE NEUMAN</t>
+          <t>LEONARD EULER CHORRILLOS</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-12.19809</t>
+          <t>-12.173963</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-77.01317</t>
+          <t>-76.99476</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>597</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>299340</t>
+          <t>781248</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>EL HOGAR</t>
+          <t>THOMAS ALVA EDISON</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-12.201</t>
+          <t>-12.20342</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-76.98906</t>
+          <t>-76.97492</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>376</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>299359</t>
+          <t>298901</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>EL MILAGRO</t>
+          <t>7052 MARIA INMACULADA</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-12.17373</t>
+          <t>-12.16532</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-77.02355</t>
+          <t>-77.02388</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>663</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>299364</t>
+          <t>725323</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>EL SEMBRADOR</t>
+          <t>BELEN</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-12.19528</t>
+          <t>-12.17445</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-76.99692</t>
+          <t>-76.99914</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>418</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3167,32 +3167,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>299415</t>
+          <t>317320</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>LIMA VILLA COLLEGE</t>
+          <t>PROLOG DE CHORRILLOS</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-12.20706</t>
+          <t>-12.20551</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-76.99944</t>
+          <t>-77.0171</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>248</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3229,37 +3229,37 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>299463</t>
+          <t>725889</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>JESUS MAESTRO</t>
+          <t>ARQUITECTO FERNANDO BELAUNDE TERRY</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-12.1985</t>
+          <t>-12.20464</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-76.99266</t>
+          <t>-77.01626</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>635</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3291,32 +3291,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>299528</t>
+          <t>833539</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>LA CASA DE CARTON</t>
+          <t>TRILCE CHORRILLOS</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-12.21233</t>
+          <t>-12.20468</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-77.00935</t>
+          <t>-77.00758</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>825</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3353,32 +3353,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>299533</t>
+          <t>298722</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>LA ESPERANZA</t>
+          <t>59 SANTA LUCIA</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-12.15546</t>
+          <t>-12.16549</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-77.01873</t>
+          <t>-77.02537</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>446</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3415,32 +3415,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>299552</t>
+          <t>299024</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>LE D'ALEMBERT</t>
+          <t>JOSE DE LA RIVA AGUERO Y OSMA</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-12.18127</t>
+          <t>-12.16639</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-76.9964</t>
+          <t>-77.0215</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>425</t>
+          <t>434</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3477,37 +3477,37 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>299608</t>
+          <t>805372</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>MARIA DE FATIMA</t>
+          <t>INNOVA SCHOOLS - CHORRILLOS UNIVERSO 2</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-12.16833</t>
+          <t>-12.17266</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-77.02407</t>
+          <t>-76.99717</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>551</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>299665</t>
+          <t>298821</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>MARIA REYNA</t>
+          <t>6153 CAPITAN DEL EJERCITO PERUANO AUGUSTO JAVIER GUTIERREZ MENDOZA</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-12.18753</t>
+          <t>-12.1904</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-77.00915</t>
+          <t>-76.9869</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>684</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>299806</t>
+          <t>299528</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>NIÑO JESUS DE PRAGA</t>
+          <t>LA CASA DE CARTON</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-12.16748</t>
+          <t>-12.21233</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-77.02466</t>
+          <t>-77.00935</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>268</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3663,32 +3663,32 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>299849</t>
+          <t>738537</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>PEDRO RUIZ GALLO</t>
+          <t>ALEPH</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-12.15798</t>
+          <t>-12.20034</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-77.02295</t>
+          <t>-77.0001</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>847</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3725,42 +3725,42 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>299887</t>
+          <t>855913</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>SAN AGUSTIN</t>
+          <t>7037 ARIOSTO MATELLINI ESPINOZA</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-12.18908</t>
+          <t>-12.16736</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>-77.01401</t>
+          <t>-76.99965</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>704</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3787,32 +3787,32 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>299892</t>
+          <t>298897</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>SAN ALFONSO</t>
+          <t>7044 SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-12.19896</t>
+          <t>-12.17302</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>-77.0027</t>
+          <t>-77.02318</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>653</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3849,32 +3849,32 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>299910</t>
+          <t>506801</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>SAN ALFONSO MARIA</t>
+          <t>7707 CRISTO REY</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-12.19916</t>
+          <t>-12.16906</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>-77.00945</t>
+          <t>-77.02996</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>461</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3911,27 +3911,27 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>300008</t>
+          <t>298802</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>SAN LUCAS</t>
+          <t>6092 LOS REYES CATOLICOS</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-12.1687</t>
+          <t>-12.18701</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>-76.99915</t>
+          <t>-77.01684</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>871</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3973,37 +3973,37 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>300027</t>
+          <t>300008</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>SAINT PATRICK'S CHILDREN</t>
+          <t>SAN LUCAS</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-12.17846</t>
+          <t>-12.1687</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>-77.01406</t>
+          <t>-76.99915</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>727</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4035,32 +4035,32 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>300107</t>
+          <t>299076</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>SANTISIMA MARIA</t>
+          <t>TUPAC AMARU II</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-12.19967</t>
+          <t>-12.19324</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>-77.00699</t>
+          <t>-76.98449</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>502</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4097,37 +4097,37 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>300112</t>
+          <t>299806</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>SANTISIMA TRINIDAD</t>
+          <t>NIÑO JESUS DE PRAGA</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-12.19227</t>
+          <t>-12.16748</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>-77.01919</t>
+          <t>-77.02466</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>509</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4159,32 +4159,32 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>300150</t>
+          <t>298859</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>SEÑOR DE LUREN</t>
+          <t>7037 ARIOSTO MATELLINI ESPINOZA</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-12.19287</t>
+          <t>-12.16701</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>-76.98384</t>
+          <t>-76.99938</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>684</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4221,32 +4221,32 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>300225</t>
+          <t>299118</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>ASOCIACION EDUCATIVA VIRGEN DE LA FAMILIA</t>
+          <t>6053 SAGRADO CORAZON</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-12.17369</t>
+          <t>-12.1609</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>-77.02416</t>
+          <t>-77.02362</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>773</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4283,32 +4283,32 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>300334</t>
+          <t>723611</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>FE Y ALEGRIA 34</t>
+          <t>SANTO DOMINGO</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-12.19328</t>
+          <t>-12.205</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>-76.98985</t>
+          <t>-77.01139</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>1081</t>
+          <t>823</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4345,32 +4345,32 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>300452</t>
+          <t>724309</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>VILLA ALARIFE</t>
+          <t>SANTO DOMINGO</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-12.20821</t>
+          <t>-12.20484</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>-77.00462</t>
+          <t>-77.01099</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>537</t>
+          <t>738</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4407,32 +4407,32 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>300517</t>
+          <t>298840</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>SAINT PATRICK'S SCHOOL</t>
+          <t>7036 ANGELICA RECHARTE CORRALES</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-12.18088</t>
+          <t>-12.16583</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>-77.01103</t>
+          <t>-77.02445</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>788</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4469,32 +4469,32 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>300621</t>
+          <t>298939</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>PALAS ATENEA</t>
+          <t>7077 LOS REYES ROJOS</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-12.16998</t>
+          <t>-12.1884</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>-76.99534</t>
+          <t>-77.0195</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>861</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4531,37 +4531,37 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>317320</t>
+          <t>299608</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>PROLOG DE CHORRILLOS</t>
+          <t>MARIA DE FATIMA</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-12.20551</t>
+          <t>-12.16833</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>-77.0171</t>
+          <t>-77.02407</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>46</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -4593,37 +4593,37 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>322543</t>
+          <t>745081</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>CORONEL JOSE JOAQUIN INCLAN</t>
+          <t>SEMILLITAS DE BUENOS AIRES DE VILLA</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>-12.17147</t>
+          <t>-12.18662</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>-77.01034</t>
+          <t>-76.99692</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>1104</t>
+          <t>29</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -4655,37 +4655,37 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>340090</t>
+          <t>906535</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>MILAGRITOS DE JESUS</t>
+          <t>MASTER SCHOOL CHORRILLOS</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>-12.19937</t>
+          <t>-12.19643</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>-76.97898</t>
+          <t>-76.99082</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>46</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -4717,32 +4717,32 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>340274</t>
+          <t>299302</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>6086 SANTA ISABEL</t>
+          <t>DIVINO MAESTRO</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>-12.20096</t>
+          <t>-12.20767</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>-76.97749</t>
+          <t>-77.0148</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>790</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4779,32 +4779,32 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>340288</t>
+          <t>322543</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>6097 MATEO PUMACAHUA</t>
+          <t>CORONEL JOSE JOAQUIN INCLAN</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>-12.19209</t>
+          <t>-12.17147</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>-76.98049</t>
+          <t>-77.01034</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>1104</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4841,32 +4841,32 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>340293</t>
+          <t>851397</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>7076 LAS BRISAS DE VILLA</t>
+          <t>SACO OLIVEROS DE SANTA ISABEL</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>-12.1973</t>
+          <t>-12.17109</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>-76.9749</t>
+          <t>-76.99497</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>2066</t>
+          <t>1240</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4903,32 +4903,32 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>342032</t>
+          <t>591333</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>YACHAYHUASI</t>
+          <t>LICEO NAVAL CAPITAN DE NAVIO JUAN FANNING GARCIA</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>-12.20267</t>
+          <t>-12.19497</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>-76.97806</t>
+          <t>-76.9892</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>500</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4965,32 +4965,32 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>506801</t>
+          <t>299415</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>7707 CRISTO REY</t>
+          <t>LIMA VILLA COLLEGE</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>-12.16906</t>
+          <t>-12.20706</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>-77.02996</t>
+          <t>-76.99944</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>524</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5027,32 +5027,32 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>537708</t>
+          <t>298883</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>CAPULLITOS DE JESUS</t>
+          <t>7042 SANTA TERESA DE VILLA</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>-12.1957</t>
+          <t>-12.18647</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>-77.02095</t>
+          <t>-77.01111</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>876</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>43</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5089,32 +5089,32 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>572711</t>
+          <t>300621</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>LOS INGENIEROS DE MATELLINI</t>
+          <t>PALAS ATENEA</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>-12.1745</t>
+          <t>-12.16998</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>-77.00303</t>
+          <t>-76.99534</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>292</t>
+          <t>754</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>43</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5151,32 +5151,32 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>582159</t>
+          <t>590442</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>LEONARD EULER CHORRILLOS</t>
+          <t>INNOVA SCHOOLS - CHORRILLOS VILLA</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>-12.173963</t>
+          <t>-12.20657</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>-76.99476</t>
+          <t>-77.00792</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>967</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5213,32 +5213,32 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>590442</t>
+          <t>754264</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>INNOVA SCHOOLS - CHORRILLOS VILLA</t>
+          <t>INNOVA SCHOOLS - CHORRILLOS LA CAMPIÑA</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>-12.20657</t>
+          <t>-12.17812</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>-77.00792</t>
+          <t>-77.00345</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>967</t>
+          <t>979</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5275,32 +5275,32 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>591333</t>
+          <t>299043</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>LICEO NAVAL CAPITAN DE NAVIO JUAN FANNING GARCIA</t>
+          <t>LOS INKAS</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>-12.19497</t>
+          <t>-12.20113</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>-76.9892</t>
+          <t>-77.01805</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>904</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>46</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -5337,32 +5337,32 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>627817</t>
+          <t>298835</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>INNOVA SCHOOLS - CHORRILLOS FAISANES</t>
+          <t>7034 ENRIQUE NERINI COLLAZOS</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>-12.17101</t>
+          <t>-12.17172</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>-76.99362</t>
+          <t>-77.024447</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>1041</t>
+          <t>849</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>48</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -5399,37 +5399,37 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>644647</t>
+          <t>300027</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>ST. GEORGE'S COLLEGE II</t>
+          <t>SAINT PATRICK'S CHILDREN</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>-12.20957</t>
+          <t>-12.17846</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>-77.00218</t>
+          <t>-77.01406</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>72</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -5461,32 +5461,32 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>723611</t>
+          <t>627817</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>SANTO DOMINGO</t>
+          <t>INNOVA SCHOOLS - CHORRILLOS FAISANES</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>-12.205</t>
+          <t>-12.17101</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>-77.01139</t>
+          <t>-76.99362</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>823</t>
+          <t>1041</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>52</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -5496,7 +5496,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5523,37 +5523,37 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>723729</t>
+          <t>905847</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>ISABEL FLORES DE OLIVA</t>
+          <t>PROLOG DE DELICIAS</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>-12.18295</t>
+          <t>-12.198064</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>-76.99897</t>
+          <t>-76.98633</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>617</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>53</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -5585,32 +5585,32 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>723833</t>
+          <t>298760</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>MAHATMA GANDHI</t>
+          <t>6075 JOSE MARIA ARGUEDAS</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>-12.20215</t>
+          <t>-12.19814</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>-76.9775</t>
+          <t>-76.98143</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>54</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5647,42 +5647,42 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>724253</t>
+          <t>298864</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>MARIANO SANTOS MATEO</t>
+          <t>7038 CORAZON DE JESUS DE ARMATAMBO</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>-12.19742</t>
+          <t>-12.1789</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>-77.02392</t>
+          <t>-77.02239</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>1067</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>54</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5709,32 +5709,32 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>724309</t>
+          <t>300334</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>SANTO DOMINGO</t>
+          <t>FE Y ALEGRIA 34</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>-12.20484</t>
+          <t>-12.19328</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>-77.01099</t>
+          <t>-76.98985</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>1081</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5771,32 +5771,32 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>725016</t>
+          <t>299081</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>DE COLORES</t>
+          <t>VIRGEN DEL MORRO SOLAR</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>-12.17403</t>
+          <t>-12.18604</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>-77.0213</t>
+          <t>-77.0179</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>1214</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>57</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5833,32 +5833,32 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>725323</t>
+          <t>300452</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>BELEN</t>
+          <t>VILLA ALARIFE</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>-12.17445</t>
+          <t>-12.20821</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>-76.99914</t>
+          <t>-77.00462</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>418</t>
+          <t>537</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5895,37 +5895,37 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>725889</t>
+          <t>299222</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>ARQUITECTO FERNANDO BELAUNDE TERRY</t>
+          <t>CHRISTIAN BARNARD</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>-12.20464</t>
+          <t>-12.1963</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>-77.01626</t>
+          <t>-76.9906</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -6019,32 +6019,32 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>738537</t>
+          <t>299199</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>ALEPH</t>
+          <t>CAMBRIDGE COLLEGE LIMA</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>-12.20034</t>
+          <t>-12.21316</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>-77.0001</t>
+          <t>-77.00384</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>847</t>
+          <t>1206</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>64</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -6081,37 +6081,37 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>745081</t>
+          <t>298798</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>SEMILLITAS DE BUENOS AIRES DE VILLA</t>
+          <t>6091 CESAR VALLEJO</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>-12.18662</t>
+          <t>-12.18918</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>-76.99692</t>
+          <t>-76.99095</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>1470</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>65</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6143,32 +6143,32 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>754264</t>
+          <t>644647</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>INNOVA SCHOOLS - CHORRILLOS LA CAMPIÑA</t>
+          <t>ST. GEORGE'S COLLEGE II</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>-12.17812</t>
+          <t>-12.20957</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>-77.00345</t>
+          <t>-77.00218</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>979</t>
+          <t>1021</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>67</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -6205,32 +6205,32 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>780654</t>
+          <t>298878</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>DIVINO MAESTRO LOS CEDROS</t>
+          <t>7039 MANUEL SCORZA TORRES</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>-12.20618</t>
+          <t>-12.18322</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>-77.01379</t>
+          <t>-76.9927</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>1372</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>70</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -6240,7 +6240,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6267,32 +6267,32 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>781248</t>
+          <t>340274</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>THOMAS ALVA EDISON</t>
+          <t>6086 SANTA ISABEL</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>-12.20342</t>
+          <t>-12.20096</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>-76.97492</t>
+          <t>-76.97749</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>70</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -6329,32 +6329,32 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>805372</t>
+          <t>298741</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>INNOVA SCHOOLS - CHORRILLOS UNIVERSO 2</t>
+          <t>7066 ANDRES AVELINO CACERES</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>-12.17266</t>
+          <t>-12.19998</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>-76.99717</t>
+          <t>-76.99325</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>71</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -6391,32 +6391,32 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>831093</t>
+          <t>298779</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>INNOVA SCHOOLS - CHORRILLOS UNIVERSO 1</t>
+          <t>6085 BRIGIDA SILVA DE OCHOA</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>-12.17103</t>
+          <t>-12.164653</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>-76.99497</t>
+          <t>-77.020892</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>1238</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>75</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -6453,32 +6453,32 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>833539</t>
+          <t>298816</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>TRILCE CHORRILLOS</t>
+          <t>6094 SANTA ROSA</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>-12.20468</t>
+          <t>-12.19016</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>-77.00758</t>
+          <t>-77.01041</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>825</t>
+          <t>1539</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>78</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -6515,32 +6515,32 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>836397</t>
+          <t>299062</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>GRACIAS JESUS</t>
+          <t>SAN PEDRO DE CHORRILLOS</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>-12.17083</t>
+          <t>-12.17363</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>-77.00035</t>
+          <t>-77.0056</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>1605</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>79</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -6550,7 +6550,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6577,42 +6577,42 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>843411</t>
+          <t>299463</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>SANTISIMA MARIA</t>
+          <t>JESUS MAESTRO</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>-12.19957</t>
+          <t>-12.1985</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>-77.00713</t>
+          <t>-76.99266</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>207</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6639,32 +6639,32 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>851397</t>
+          <t>298736</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>SACO OLIVEROS DE SANTA ISABEL</t>
+          <t>6005 GENERAL EMILIO SOYER CABERO</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>-12.17109</t>
+          <t>-12.16355</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>-76.99497</t>
+          <t>-77.02045</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>1240</t>
+          <t>1246</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>80</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -6701,32 +6701,32 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>855913</t>
+          <t>298915</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>7037 ARIOSTO MATELLINI ESPINOZA</t>
+          <t>7064 MARIA AUXILIADORA</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>-12.16736</t>
+          <t>-12.18774</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>-76.99965</t>
+          <t>-77.00494</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>704</t>
+          <t>1884</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>80</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -6736,7 +6736,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6763,32 +6763,32 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>858365</t>
+          <t>340293</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>YACHAYHUASI</t>
+          <t>7076 LAS BRISAS DE VILLA</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>-12.20389</t>
+          <t>-12.1973</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>-76.97946</t>
+          <t>-76.9749</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>2066</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>89</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -6825,37 +6825,37 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>904287</t>
+          <t>299887</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>LOS INGENIEROS DE SAN MARCOS</t>
+          <t>SAN AGUSTIN</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>-12.195404</t>
+          <t>-12.18908</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>-77.013195</t>
+          <t>-77.01401</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>140</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -6887,32 +6887,32 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>905847</t>
+          <t>340288</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>PROLOG DE DELICIAS</t>
+          <t>6097 MATEO PUMACAHUA</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>-12.198064</t>
+          <t>-12.19209</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>-76.98633</t>
+          <t>-76.98049</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>94</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -6949,37 +6949,37 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>906535</t>
+          <t>298920</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>MASTER SCHOOL CHORRILLOS</t>
+          <t>7075 JUAN PABLO II</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>-12.19643</t>
+          <t>-12.1944</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>-76.99082</t>
+          <t>-77.01946</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>2097</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>97</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">

--- a/ZonasEscolares/excels/LIMA-LIMA-CHORRILLOS.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-CHORRILLOS.xlsx
@@ -501,37 +501,37 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>298963</t>
+          <t>906535</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>LOS ANGELITOS DEL DIVINO NIÑO</t>
+          <t>MASTER SCHOOL CHORRILLOS</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-12.20061</t>
+          <t>46</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-76.98792</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>-12.19643</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-76.99082</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -563,37 +563,37 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>300112</t>
+          <t>905847</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SANTISIMA TRINIDAD</t>
+          <t>PROLOG DE DELICIAS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-12.19227</t>
+          <t>617</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-77.01919</t>
+          <t>53</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>-12.198064</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-76.98633</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>836397</t>
+          <t>904287</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>GRACIAS JESUS</t>
+          <t>LOS INGENIEROS DE SAN MARCOS</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-12.17083</t>
+          <t>306</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-77.00035</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>-12.195404</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-77.013195</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>298944</t>
+          <t>858365</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>7103 PEDRO PAULET Y MOSTAJO</t>
+          <t>YACHAYHUASI</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-12.20491</t>
+          <t>272</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-76.97649</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>-12.20389</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-76.97946</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>298996</t>
+          <t>855913</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>COMUNAL SANTA TERESA</t>
+          <t>7037 ARIOSTO MATELLINI ESPINOZA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-12.18678</t>
+          <t>704</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-77.01719</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>-12.16736</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-76.99965</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>298784</t>
+          <t>851397</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>6090 JOSE OLAYA BALANDRA</t>
+          <t>SACO OLIVEROS DE SANTA ISABEL</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-12.19442</t>
+          <t>1240</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-77.0063</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2685</t>
+          <t>-12.17109</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>-76.99497</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>298958</t>
+          <t>843411</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>BUENOS AIRES DE VILLA</t>
+          <t>SANTISIMA MARIA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-12.18745</t>
+          <t>332</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-76.99716</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>-12.19957</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-77.00713</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>298623</t>
+          <t>836397</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>518 LOS ANGELES DE JESUS</t>
+          <t>GRACIAS JESUS</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-12.17658</t>
+          <t>217</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-77.0094</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>-12.17083</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-77.00035</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>299892</t>
+          <t>833539</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SAN ALFONSO</t>
+          <t>TRILCE CHORRILLOS</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-12.19896</t>
+          <t>825</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-77.0027</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>-12.20468</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-77.00758</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>299910</t>
+          <t>831093</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SAN ALFONSO MARIA</t>
+          <t>INNOVA SCHOOLS - CHORRILLOS UNIVERSO 1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-12.19916</t>
+          <t>370</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-77.00945</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>-12.17103</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-76.99497</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>725016</t>
+          <t>805372</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>DE COLORES</t>
+          <t>INNOVA SCHOOLS - CHORRILLOS UNIVERSO 2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-12.17403</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-77.0213</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>-12.17266</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-76.99717</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>299849</t>
+          <t>781248</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>PEDRO RUIZ GALLO</t>
+          <t>THOMAS ALVA EDISON</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-12.15798</t>
+          <t>376</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-77.02295</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>-12.20342</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>-76.97492</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>723833</t>
+          <t>780654</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MAHATMA GANDHI</t>
+          <t>DIVINO MAESTRO LOS CEDROS</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-12.20215</t>
+          <t>299</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-76.9775</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>-12.20618</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-77.01379</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>299533</t>
+          <t>754264</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>LA ESPERANZA</t>
+          <t>INNOVA SCHOOLS - CHORRILLOS LA CAMPIÑA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-12.15546</t>
+          <t>979</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-77.01873</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>-12.17812</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-77.00345</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,37 +1369,37 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>537708</t>
+          <t>745081</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CAPULLITOS DE JESUS</t>
+          <t>SEMILLITAS DE BUENOS AIRES DE VILLA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-12.1957</t>
+          <t>29</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-77.02095</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>-12.18662</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-76.99692</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>572711</t>
+          <t>738537</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>LOS INGENIEROS DE MATELLINI</t>
+          <t>ALEPH</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-12.1745</t>
+          <t>847</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-77.00303</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>292</t>
+          <t>-12.20034</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-77.0001</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,37 +1493,37 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>299340</t>
+          <t>725926</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>EL HOGAR</t>
+          <t>SEMILLITAS DEL FUTURO</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-12.201</t>
+          <t>69</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-76.98906</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>-12.18766</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-76.99101</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>300150</t>
+          <t>725889</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SEÑOR DE LUREN</t>
+          <t>ARQUITECTO FERNANDO BELAUNDE TERRY</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-12.19287</t>
+          <t>635</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-76.98384</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>-12.20464</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-77.01626</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>298982</t>
+          <t>725323</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>COMUNAL SANTA ISABEL DE VILLA</t>
+          <t>BELEN</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-12.20091</t>
+          <t>418</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-76.97847</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>344</t>
+          <t>-12.17445</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-76.99914</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>299364</t>
+          <t>725016</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>EL SEMBRADOR</t>
+          <t>DE COLORES</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-12.19528</t>
+          <t>242</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-76.99692</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>-12.17403</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-77.0213</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>780654</t>
+          <t>724309</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>DIVINO MAESTRO LOS CEDROS</t>
+          <t>SANTO DOMINGO</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-12.20618</t>
+          <t>738</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-77.01379</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>-12.20484</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-77.01099</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,37 +1803,37 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>858365</t>
+          <t>724253</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>YACHAYHUASI</t>
+          <t>MARIANO SANTOS MATEO</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-12.20389</t>
+          <t>185</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-76.97946</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>-12.19742</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-77.02392</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>298637</t>
+          <t>723833</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>VIRGEN MARIA MADRE DE LOS NIÑOS</t>
+          <t>MAHATMA GANDHI</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-12.19044</t>
+          <t>231</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-77.01063</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>-12.20215</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-76.9775</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,37 +1927,37 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>299335</t>
+          <t>723729</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MARIA REICHE GROSSE NEUMAN</t>
+          <t>ISABEL FLORES DE OLIVA</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-12.19809</t>
+          <t>137</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-77.01317</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>-12.18295</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-76.99897</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>300107</t>
+          <t>723611</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>SANTISIMA MARIA</t>
+          <t>SANTO DOMINGO</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-12.19967</t>
+          <t>823</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-77.00699</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>-12.205</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-77.01139</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>340090</t>
+          <t>644647</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MILAGRITOS DE JESUS</t>
+          <t>ST. GEORGE'S COLLEGE II</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-12.19937</t>
+          <t>1021</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-76.97898</t>
+          <t>67</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>-12.20957</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-77.00218</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>342032</t>
+          <t>627817</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>YACHAYHUASI</t>
+          <t>INNOVA SCHOOLS - CHORRILLOS FAISANES</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-12.20267</t>
+          <t>1041</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-76.97806</t>
+          <t>52</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>-12.17101</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-76.99362</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>843411</t>
+          <t>591333</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>SANTISIMA MARIA</t>
+          <t>LICEO NAVAL CAPITAN DE NAVIO JUAN FANNING GARCIA</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-12.19957</t>
+          <t>500</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-77.00713</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>-12.19497</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-76.9892</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>298977</t>
+          <t>590442</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>COMUNAL SAN JUAN DE LA LIBERTAD</t>
+          <t>INNOVA SCHOOLS - CHORRILLOS VILLA</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-12.19071</t>
+          <t>967</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-76.98651</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>-12.20657</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-77.00792</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>299359</t>
+          <t>582159</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>EL MILAGRO</t>
+          <t>LEONARD EULER CHORRILLOS</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-12.17373</t>
+          <t>597</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-77.02355</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>-12.173963</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-76.99476</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>904287</t>
+          <t>572711</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>LOS INGENIEROS DE SAN MARCOS</t>
+          <t>LOS INGENIEROS DE MATELLINI</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-12.195404</t>
+          <t>292</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-77.013195</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>-12.1745</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-77.00303</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>299284</t>
+          <t>537708</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CRISTO REDENTOR</t>
+          <t>CAPULLITOS DE JESUS</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-12.19323</t>
+          <t>302</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-77.01253</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>-12.1957</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-77.02095</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>299665</t>
+          <t>506801</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>MARIA REYNA</t>
+          <t>7707 CRISTO REY</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-12.18753</t>
+          <t>461</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-77.00915</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>-12.16906</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-77.02996</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>300225</t>
+          <t>342032</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ASOCIACION EDUCATIVA VIRGEN DE LA FAMILIA</t>
+          <t>YACHAYHUASI</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-12.17369</t>
+          <t>252</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-77.02416</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>-12.20267</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-76.97806</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,37 +2609,37 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>724253</t>
+          <t>340293</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>MARIANO SANTOS MATEO</t>
+          <t>7076 LAS BRISAS DE VILLA</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-12.19742</t>
+          <t>2066</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-77.02392</t>
+          <t>89</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>-12.1973</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-76.9749</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>299552</t>
+          <t>340288</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>LE D'ALEMBERT</t>
+          <t>6097 MATEO PUMACAHUA</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-12.18127</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-76.9964</t>
+          <t>94</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>425</t>
+          <t>-12.19209</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-76.98049</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,37 +2733,37 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>723729</t>
+          <t>340274</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>ISABEL FLORES DE OLIVA</t>
+          <t>6086 SANTA ISABEL</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-12.18295</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-76.99897</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>-12.20096</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-76.97749</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>831093</t>
+          <t>340090</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>INNOVA SCHOOLS - CHORRILLOS UNIVERSO 1</t>
+          <t>MILAGRITOS DE JESUS</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-12.17103</t>
+          <t>381</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-76.99497</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>-12.19937</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-76.97898</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>300517</t>
+          <t>322543</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>SAINT PATRICK'S SCHOOL</t>
+          <t>CORONEL JOSE JOAQUIN INCLAN</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-12.18088</t>
+          <t>1104</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-77.01103</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>-12.17147</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-77.01034</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>582159</t>
+          <t>317320</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>LEONARD EULER CHORRILLOS</t>
+          <t>PROLOG DE CHORRILLOS</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-12.173963</t>
+          <t>248</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-76.99476</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>-12.20551</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-77.0171</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>781248</t>
+          <t>300621</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>THOMAS ALVA EDISON</t>
+          <t>PALAS ATENEA</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-12.20342</t>
+          <t>754</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-76.97492</t>
+          <t>43</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>-12.16998</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-76.99534</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>298901</t>
+          <t>300517</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>7052 MARIA INMACULADA</t>
+          <t>SAINT PATRICK'S SCHOOL</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-12.16532</t>
+          <t>455</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-77.02388</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>-12.18088</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-77.01103</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>725323</t>
+          <t>300452</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>BELEN</t>
+          <t>VILLA ALARIFE</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-12.17445</t>
+          <t>537</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-76.99914</t>
+          <t>59</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>418</t>
+          <t>-12.20821</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-77.00462</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3167,32 +3167,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>317320</t>
+          <t>300334</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>PROLOG DE CHORRILLOS</t>
+          <t>FE Y ALEGRIA 34</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-12.20551</t>
+          <t>1081</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-77.0171</t>
+          <t>55</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>-12.19328</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-76.98985</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>725889</t>
+          <t>300225</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>ARQUITECTO FERNANDO BELAUNDE TERRY</t>
+          <t>ASOCIACION EDUCATIVA VIRGEN DE LA FAMILIA</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-12.20464</t>
+          <t>260</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-77.01626</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>-12.17369</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-77.02416</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3291,32 +3291,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>833539</t>
+          <t>300150</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>TRILCE CHORRILLOS</t>
+          <t>SEÑOR DE LUREN</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-12.20468</t>
+          <t>245</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-77.00758</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>825</t>
+          <t>-12.19287</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-76.98384</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3353,37 +3353,37 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>298722</t>
+          <t>300112</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>59 SANTA LUCIA</t>
+          <t>SANTISIMA TRINIDAD</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-12.16549</t>
+          <t>69</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-77.02537</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>446</t>
+          <t>-12.19227</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-77.01919</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3415,32 +3415,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>299024</t>
+          <t>300107</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>JOSE DE LA RIVA AGUERO Y OSMA</t>
+          <t>SANTISIMA MARIA</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-12.16639</t>
+          <t>307</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-77.0215</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>434</t>
+          <t>-12.19967</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-77.00699</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3477,37 +3477,37 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>805372</t>
+          <t>300027</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>INNOVA SCHOOLS - CHORRILLOS UNIVERSO 2</t>
+          <t>SAINT PATRICK'S CHILDREN</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-12.17266</t>
+          <t>72</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-76.99717</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>-12.17846</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-77.01406</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>298821</t>
+          <t>300008</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>6153 CAPITAN DEL EJERCITO PERUANO AUGUSTO JAVIER GUTIERREZ MENDOZA</t>
+          <t>SAN LUCAS</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-12.1904</t>
+          <t>727</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-76.9869</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>-12.1687</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-76.99915</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>299528</t>
+          <t>299910</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>LA CASA DE CARTON</t>
+          <t>SAN ALFONSO MARIA</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-12.21233</t>
+          <t>308</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-77.00935</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>-12.19916</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-77.00945</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3663,32 +3663,32 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>738537</t>
+          <t>299892</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>ALEPH</t>
+          <t>SAN ALFONSO</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-12.20034</t>
+          <t>248</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-77.0001</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>847</t>
+          <t>-12.19896</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-77.0027</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3725,42 +3725,42 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>855913</t>
+          <t>299887</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>7037 ARIOSTO MATELLINI ESPINOZA</t>
+          <t>SAN AGUSTIN</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-12.16736</t>
+          <t>140</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>-76.99965</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>704</t>
+          <t>-12.18908</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-77.01401</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3787,32 +3787,32 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>298897</t>
+          <t>299849</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>7044 SAN MARTIN DE PORRES</t>
+          <t>PEDRO RUIZ GALLO</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-12.17302</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>-77.02318</t>
+          <t>132</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>-12.15798</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>-77.02295</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3849,32 +3849,32 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>506801</t>
+          <t>299806</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>7707 CRISTO REY</t>
+          <t>NIÑO JESUS DE PRAGA</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-12.16906</t>
+          <t>509</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>-77.02996</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>-12.16748</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>-77.02466</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3911,32 +3911,32 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>298802</t>
+          <t>299665</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>6092 LOS REYES CATOLICOS</t>
+          <t>MARIA REYNA</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-12.18701</t>
+          <t>245</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>-77.01684</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>871</t>
+          <t>-12.18753</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-77.00915</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3973,37 +3973,37 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>300008</t>
+          <t>299608</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>SAN LUCAS</t>
+          <t>MARIA DE FATIMA</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-12.1687</t>
+          <t>46</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>-76.99915</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>-12.16833</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-77.02407</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4035,32 +4035,32 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>299076</t>
+          <t>299552</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>TUPAC AMARU II</t>
+          <t>LE D'ALEMBERT</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-12.19324</t>
+          <t>425</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>-76.98449</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>502</t>
+          <t>-12.18127</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>-76.9964</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4097,32 +4097,32 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>299806</t>
+          <t>299533</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>NIÑO JESUS DE PRAGA</t>
+          <t>LA ESPERANZA</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-12.16748</t>
+          <t>233</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>-77.02466</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>-12.15546</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>-77.01873</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4159,32 +4159,32 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>298859</t>
+          <t>299528</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>7037 ARIOSTO MATELLINI ESPINOZA</t>
+          <t>LA CASA DE CARTON</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-12.16701</t>
+          <t>268</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>-76.99938</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>-12.21233</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>-77.00935</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4221,37 +4221,37 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>299118</t>
+          <t>299463</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>6053 SAGRADO CORAZON</t>
+          <t>JESUS MAESTRO</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-12.1609</t>
+          <t>207</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>-77.02362</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>773</t>
+          <t>-12.1985</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>-76.99266</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4283,32 +4283,32 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>723611</t>
+          <t>299415</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>SANTO DOMINGO</t>
+          <t>LIMA VILLA COLLEGE</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-12.205</t>
+          <t>524</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>-77.01139</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>823</t>
+          <t>-12.20706</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>-76.99944</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4345,32 +4345,32 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>724309</t>
+          <t>299364</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>SANTO DOMINGO</t>
+          <t>EL SEMBRADOR</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-12.20484</t>
+          <t>302</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>-77.01099</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>-12.19528</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>-76.99692</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4407,32 +4407,32 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>298840</t>
+          <t>299359</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>7036 ANGELICA RECHARTE CORRALES</t>
+          <t>EL MILAGRO</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-12.16583</t>
+          <t>203</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>-77.02445</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>-12.17373</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>-77.02355</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4469,32 +4469,32 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>298939</t>
+          <t>299340</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>7077 LOS REYES ROJOS</t>
+          <t>EL HOGAR</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-12.1884</t>
+          <t>271</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>-77.0195</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>-12.201</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>-76.98906</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4531,37 +4531,37 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>299608</t>
+          <t>299335</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>MARIA DE FATIMA</t>
+          <t>MARIA REICHE GROSSE NEUMAN</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-12.16833</t>
+          <t>248</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>-77.02407</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>-12.19809</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-77.01317</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -4593,42 +4593,42 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>745081</t>
+          <t>299302</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>SEMILLITAS DE BUENOS AIRES DE VILLA</t>
+          <t>DIVINO MAESTRO</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>-12.18662</t>
+          <t>790</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>-76.99692</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-12.20767</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-77.0148</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4655,37 +4655,37 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>906535</t>
+          <t>299284</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>MASTER SCHOOL CHORRILLOS</t>
+          <t>CRISTO REDENTOR</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>-12.19643</t>
+          <t>247</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>-76.99082</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>-12.19323</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-77.01253</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -4717,42 +4717,42 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>299302</t>
+          <t>299222</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>DIVINO MAESTRO</t>
+          <t>CHRISTIAN BARNARD</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>-12.20767</t>
+          <t>37</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>-77.0148</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>790</t>
+          <t>-12.1963</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>-76.9906</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4779,32 +4779,32 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>322543</t>
+          <t>299199</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>CORONEL JOSE JOAQUIN INCLAN</t>
+          <t>CAMBRIDGE COLLEGE LIMA</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>-12.17147</t>
+          <t>1206</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>-77.01034</t>
+          <t>64</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>1104</t>
+          <t>-12.21316</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>-77.00384</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4841,32 +4841,32 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>851397</t>
+          <t>299118</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>SACO OLIVEROS DE SANTA ISABEL</t>
+          <t>6053 SAGRADO CORAZON</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>-12.17109</t>
+          <t>773</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>-76.99497</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>1240</t>
+          <t>-12.1609</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>-77.02362</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4903,32 +4903,32 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>591333</t>
+          <t>299081</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>LICEO NAVAL CAPITAN DE NAVIO JUAN FANNING GARCIA</t>
+          <t>VIRGEN DEL MORRO SOLAR</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>-12.19497</t>
+          <t>1214</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>-76.9892</t>
+          <t>57</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>-12.18604</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>-77.0179</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4965,32 +4965,32 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>299415</t>
+          <t>299076</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>LIMA VILLA COLLEGE</t>
+          <t>TUPAC AMARU II</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>-12.20706</t>
+          <t>502</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>-76.99944</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>-12.19324</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>-76.98449</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5027,32 +5027,32 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>298883</t>
+          <t>299062</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>7042 SANTA TERESA DE VILLA</t>
+          <t>SAN PEDRO DE CHORRILLOS</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>-12.18647</t>
+          <t>1605</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>-77.01111</t>
+          <t>79</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>-12.17363</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>-77.0056</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5062,7 +5062,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5089,32 +5089,32 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>300621</t>
+          <t>299043</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>PALAS ATENEA</t>
+          <t>LOS INKAS</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>-12.16998</t>
+          <t>904</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>-76.99534</t>
+          <t>46</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>-12.20113</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>-77.01805</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5151,32 +5151,32 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>590442</t>
+          <t>299024</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>INNOVA SCHOOLS - CHORRILLOS VILLA</t>
+          <t>JOSE DE LA RIVA AGUERO Y OSMA</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>-12.20657</t>
+          <t>434</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>-77.00792</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>967</t>
+          <t>-12.16639</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>-77.0215</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5213,32 +5213,32 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>754264</t>
+          <t>298996</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>INNOVA SCHOOLS - CHORRILLOS LA CAMPIÑA</t>
+          <t>COMUNAL SANTA TERESA</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>-12.17812</t>
+          <t>201</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>-77.00345</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>979</t>
+          <t>-12.18678</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>-77.01719</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5275,32 +5275,32 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>299043</t>
+          <t>298982</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>LOS INKAS</t>
+          <t>COMUNAL SANTA ISABEL DE VILLA</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>-12.20113</t>
+          <t>344</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>-77.01805</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>904</t>
+          <t>-12.20091</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>-76.97847</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -5337,32 +5337,32 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>298835</t>
+          <t>298977</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>7034 ENRIQUE NERINI COLLAZOS</t>
+          <t>COMUNAL SAN JUAN DE LA LIBERTAD</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>-12.17172</t>
+          <t>383</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>-77.024447</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>849</t>
+          <t>-12.19071</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>-76.98651</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -5372,7 +5372,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5399,37 +5399,37 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>300027</t>
+          <t>298963</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>SAINT PATRICK'S CHILDREN</t>
+          <t>LOS ANGELITOS DEL DIVINO NIÑO</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>-12.17846</t>
+          <t>213</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>-77.01406</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>-12.20061</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>-76.98792</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -5461,32 +5461,32 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>627817</t>
+          <t>298958</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>INNOVA SCHOOLS - CHORRILLOS FAISANES</t>
+          <t>BUENOS AIRES DE VILLA</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>-12.17101</t>
+          <t>213</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>-76.99362</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>1041</t>
+          <t>-12.18745</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>-76.99716</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -5496,7 +5496,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5523,32 +5523,32 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>905847</t>
+          <t>298944</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>PROLOG DE DELICIAS</t>
+          <t>7103 PEDRO PAULET Y MOSTAJO</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>-12.198064</t>
+          <t>236</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>-76.98633</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>-12.20491</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>-76.97649</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -5585,32 +5585,32 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>298760</t>
+          <t>298939</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>6075 JOSE MARIA ARGUEDAS</t>
+          <t>7077 LOS REYES ROJOS</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>-12.19814</t>
+          <t>861</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>-76.98143</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>-12.1884</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>-77.0195</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5647,32 +5647,32 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>298864</t>
+          <t>298920</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>7038 CORAZON DE JESUS DE ARMATAMBO</t>
+          <t>7075 JUAN PABLO II</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>-12.1789</t>
+          <t>2097</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>-77.02239</t>
+          <t>97</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>1067</t>
+          <t>-12.1944</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>-77.01946</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5682,7 +5682,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5709,32 +5709,32 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>300334</t>
+          <t>298915</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>FE Y ALEGRIA 34</t>
+          <t>7064 MARIA AUXILIADORA</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>-12.19328</t>
+          <t>1884</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>-76.98985</t>
+          <t>80</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>1081</t>
+          <t>-12.18774</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>-77.00494</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5771,32 +5771,32 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>299081</t>
+          <t>298901</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>VIRGEN DEL MORRO SOLAR</t>
+          <t>7052 MARIA INMACULADA</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>-12.18604</t>
+          <t>663</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>-77.0179</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>1214</t>
+          <t>-12.16532</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>-77.02388</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5833,32 +5833,32 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>300452</t>
+          <t>298897</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>VILLA ALARIFE</t>
+          <t>7044 SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>-12.20821</t>
+          <t>653</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>-77.00462</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>537</t>
+          <t>-12.17302</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>-77.02318</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5895,37 +5895,37 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>299222</t>
+          <t>298883</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>CHRISTIAN BARNARD</t>
+          <t>7042 SANTA TERESA DE VILLA</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>-12.1963</t>
+          <t>876</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>-76.9906</t>
+          <t>43</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>-12.18647</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>-77.01111</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -5957,42 +5957,42 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>725926</t>
+          <t>298878</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>SEMILLITAS DEL FUTURO</t>
+          <t>7039 MANUEL SCORZA TORRES</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>-12.18766</t>
+          <t>1372</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>-76.99101</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>-12.18322</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>-76.9927</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6019,32 +6019,32 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>299199</t>
+          <t>298864</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>CAMBRIDGE COLLEGE LIMA</t>
+          <t>7038 CORAZON DE JESUS DE ARMATAMBO</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>-12.21316</t>
+          <t>1067</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>-77.00384</t>
+          <t>54</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>1206</t>
+          <t>-12.1789</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>-77.02239</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6081,32 +6081,32 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>298798</t>
+          <t>298859</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>6091 CESAR VALLEJO</t>
+          <t>7037 ARIOSTO MATELLINI ESPINOZA</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>-12.18918</t>
+          <t>684</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>-76.99095</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>1470</t>
+          <t>-12.16701</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>-76.99938</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -6143,32 +6143,32 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>644647</t>
+          <t>298840</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>ST. GEORGE'S COLLEGE II</t>
+          <t>7036 ANGELICA RECHARTE CORRALES</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>-12.20957</t>
+          <t>788</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>-77.00218</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>-12.16583</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>-77.02445</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -6205,32 +6205,32 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>298878</t>
+          <t>298835</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>7039 MANUEL SCORZA TORRES</t>
+          <t>7034 ENRIQUE NERINI COLLAZOS</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>-12.18322</t>
+          <t>849</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>-76.9927</t>
+          <t>48</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>1372</t>
+          <t>-12.17172</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>-77.024447</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -6267,32 +6267,32 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>340274</t>
+          <t>298821</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>6086 SANTA ISABEL</t>
+          <t>6153 CAPITAN DEL EJERCITO PERUANO AUGUSTO JAVIER GUTIERREZ MENDOZA</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>-12.20096</t>
+          <t>684</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>-76.97749</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>-12.1904</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>-76.9869</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -6329,32 +6329,32 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>298741</t>
+          <t>298816</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>7066 ANDRES AVELINO CACERES</t>
+          <t>6094 SANTA ROSA</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>-12.19998</t>
+          <t>1539</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>-76.99325</t>
+          <t>78</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>-12.19016</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>-77.01041</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -6391,32 +6391,32 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>298779</t>
+          <t>298802</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>6085 BRIGIDA SILVA DE OCHOA</t>
+          <t>6092 LOS REYES CATOLICOS</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>-12.164653</t>
+          <t>871</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>-77.020892</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>1238</t>
+          <t>-12.18701</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>-77.01684</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -6453,32 +6453,32 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>298816</t>
+          <t>298798</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>6094 SANTA ROSA</t>
+          <t>6091 CESAR VALLEJO</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>-12.19016</t>
+          <t>1470</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>-77.01041</t>
+          <t>65</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>1539</t>
+          <t>-12.18918</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>-76.99095</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -6515,32 +6515,32 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>299062</t>
+          <t>298784</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>SAN PEDRO DE CHORRILLOS</t>
+          <t>6090 JOSE OLAYA BALANDRA</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>-12.17363</t>
+          <t>2685</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>-77.0056</t>
+          <t>113</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>1605</t>
+          <t>-12.19442</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>-77.0063</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -6577,37 +6577,37 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>299463</t>
+          <t>298779</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>JESUS MAESTRO</t>
+          <t>6085 BRIGIDA SILVA DE OCHOA</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>-12.1985</t>
+          <t>1238</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>-76.99266</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>-12.164653</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-77.020892</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>298736</t>
+          <t>298760</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>6005 GENERAL EMILIO SOYER CABERO</t>
+          <t>6075 JOSE MARIA ARGUEDAS</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>-12.16355</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>-77.02045</t>
+          <t>54</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>-12.19814</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>-76.98143</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -6701,32 +6701,32 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>298915</t>
+          <t>298741</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>7064 MARIA AUXILIADORA</t>
+          <t>7066 ANDRES AVELINO CACERES</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>-12.18774</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>-77.00494</t>
+          <t>71</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>1884</t>
+          <t>-12.19998</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>-76.99325</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -6763,32 +6763,32 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>340293</t>
+          <t>298736</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>7076 LAS BRISAS DE VILLA</t>
+          <t>6005 GENERAL EMILIO SOYER CABERO</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>-12.1973</t>
+          <t>1246</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>-76.9749</t>
+          <t>80</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>2066</t>
+          <t>-12.16355</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>-77.02045</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -6825,37 +6825,37 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>299887</t>
+          <t>298722</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>SAN AGUSTIN</t>
+          <t>59 SANTA LUCIA</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>-12.18908</t>
+          <t>446</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>-77.01401</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>-12.16549</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-77.02537</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -6887,32 +6887,32 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>340288</t>
+          <t>298637</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>6097 MATEO PUMACAHUA</t>
+          <t>VIRGEN MARIA MADRE DE LOS NIÑOS</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>-12.19209</t>
+          <t>410</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>-76.98049</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>-12.19044</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>-77.01063</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -6949,32 +6949,32 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>298920</t>
+          <t>298623</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>7075 JUAN PABLO II</t>
+          <t>518 LOS ANGELES DE JESUS</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>-12.1944</t>
+          <t>278</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>-77.01946</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>2097</t>
+          <t>-12.17658</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>-77.0094</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">

--- a/ZonasEscolares/excels/LIMA-LIMA-CHORRILLOS.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-CHORRILLOS.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
